--- a/V1.0需求（2026.6.11）/官方数据/DW_专业建设数据模型设计_岗位所属行业更新.xlsx
+++ b/V1.0需求（2026.6.11）/官方数据/DW_专业建设数据模型设计_岗位所属行业更新.xlsx
@@ -2,26 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_总览" sheetId="1" r:id="Raba1a04d523d4961"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_专业库" sheetId="2" r:id="Rd8d4d4208d284412"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_行业库" sheetId="3" r:id="Rd3f3a1f1dd7e4599"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_产业链库" sheetId="4" r:id="Rfbdbbc62609c4434"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_产业环节库" sheetId="5" r:id="R2a582267113c4f54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04A_产业环节关系库" sheetId="6" r:id="Raec11f687b684dec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_职业库" sheetId="7" r:id="R9ed7db33569e4b84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_岗位库" sheetId="8" r:id="R9bd0efbe35674bd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_岗位任务库" sheetId="9" r:id="Raed65053ff6246cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_岗位能力库" sheetId="10" r:id="R15c5d87efe954174"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_企业库" sheetId="11" r:id="R502db7f61d774f7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_招聘信息库" sheetId="12" r:id="Rc71b6872c89d48de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_招聘趋势库" sheetId="13" r:id="Ra334a186846f4edd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_赛事库" sheetId="14" r:id="Rf501b1014f214446"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_证书库" sheetId="15" r:id="R50117f7e30774569"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_课程库" sheetId="16" r:id="Ra3ca90f5cb044b5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_政策库" sheetId="17" r:id="R95daaf924f95411b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_初始化批次库" sheetId="18" r:id="Rb296d8e36b504109"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_数据来源目录" sheetId="19" r:id="Re7a0306683284f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_关联关系" sheetId="20" r:id="Rd18f6ba7849a4b59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_总览" sheetId="1" r:id="R87df9525d9e349cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_专业库" sheetId="2" r:id="R3af34b0bf9564d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_行业库" sheetId="3" r:id="R99323a3891e24af2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_产业链库" sheetId="4" r:id="R5e0c96d8d982400f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_产业环节库" sheetId="5" r:id="Rb40c7d4c75314209"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04A_产业环节关系库" sheetId="6" r:id="R0ea90bfe2e714969"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_职业库" sheetId="7" r:id="R189167a99d064858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_岗位库" sheetId="8" r:id="Rf655683dadf4485d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06A_岗位资源匹配库" sheetId="9" r:id="R8a53c251a7284d01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_岗位任务库" sheetId="10" r:id="R759d9ad0b02f48d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_岗位能力库" sheetId="11" r:id="R08461603aa684a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_企业库" sheetId="12" r:id="R266c169e8a174faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_招聘信息库" sheetId="13" r:id="R684342c0dea740fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_招聘趋势库" sheetId="14" r:id="Ra452bf7a47c14866"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11A_新技术岗位匹配库" sheetId="15" r:id="R74c0aea720304ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_赛事库" sheetId="16" r:id="R4b933eca33a64e42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_证书库" sheetId="17" r:id="R5182bdcc9c254fec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_课程库" sheetId="18" r:id="R74e94268d3f44d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_政策库" sheetId="19" r:id="R009737da634f46cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_初始化批次库" sheetId="20" r:id="R0162b8ed7ec14633"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_数据来源目录" sheetId="21" r:id="R287e6876a16f4320"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_关联关系" sheetId="22" r:id="R1fb86b84758e4ec4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -467,10 +469,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>ability_id</x:v>
+        <x:v>task_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>能力项ID</x:v>
+        <x:v>任务ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>string</x:v>
@@ -482,10 +484,10 @@
         <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>能力项主键。</x:v>
+        <x:v>岗位典型工作任务主键。</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>ability_bim_model</x:v>
+        <x:v>task_bim_001</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
         <x:v>系统生成/模板导入</x:v>
@@ -529,10 +531,10 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>ability_name</x:v>
+        <x:v>task_name</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>能力项名称</x:v>
+        <x:v>任务名称</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>string</x:v>
@@ -544,190 +546,132 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>能力项标准名称，同岗位下不重复。</x:v>
+        <x:v>典型工作任务名称。</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>BIM模型深化能力</x:v>
+        <x:v>BIM模型深化与碰撞检查</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>岗位画像/能力模板</x:v>
+        <x:v>岗位画像/模板导入</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
         <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
     </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
+    <x:row r="5" ht="24" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>ability_category</x:v>
+        <x:v>task_description</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>能力类别</x:v>
+        <x:v>任务描述</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str"/>
+      <x:c r="F5" s="11" t="str">
+        <x:v>任务工作内容、输入输出、交付标准。</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>基于施工图完成模型深化并输出碰撞报告</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str">
+        <x:v>招聘文本/专家维护</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="str">
+        <x:v>按版本</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="str"/>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="12" t="str">
+        <x:v>task_stage</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>任务阶段</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
         <x:v>enum</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="str">
-        <x:v>知识、技能、素养。</x:v>
-      </x:c>
-      <x:c r="G5" s="11" t="str">
-        <x:v>技能</x:v>
-      </x:c>
-      <x:c r="H5" s="11" t="str">
-        <x:v>岗位中心</x:v>
-      </x:c>
-      <x:c r="I5" s="11" t="str">
-        <x:v>按项目维护</x:v>
-      </x:c>
-      <x:c r="J5" s="11" t="str"/>
-    </x:row>
-    <x:row r="6" ht="24" hidden="0" customHeight="1">
-      <x:c r="A6" s="12" t="str">
-        <x:v>definition</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="str">
-        <x:v>能力定义</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>text</x:v>
-      </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str">
-        <x:v>能力项内涵和边界。</x:v>
+        <x:v>准备、实施、检查、交付、运维等。</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>能够基于专业软件完成模型深化与构件信息维护</x:v>
+        <x:v>实施</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>专家维护/AI生成后审核</x:v>
+        <x:v>人工维护</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>按版本</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str"/>
     </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
+    <x:row r="7" ht="24" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>normalized_name</x:v>
+        <x:v>ability_ids</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>标准化名称</x:v>
+        <x:v>关联能力项</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+      <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str">
-        <x:v>用于与招聘技能热度、课程能力映射的统一名称。</x:v>
+        <x:v>完成任务所需能力项ID列表。</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>BIM深化设计</x:v>
+        <x:v>ability_bim_model,ability_issue_report</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>规则归一/人工复核</x:v>
+        <x:v>岗位能力库</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="str"/>
+        <x:v>按项目维护</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str">
+        <x:v>多值可拆关系表</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>score</x:v>
+        <x:v>evidence_source</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>能力强度</x:v>
+        <x:v>证据来源</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str">
-        <x:v>岗位画像或雷达图使用的能力强度。</x:v>
+        <x:v>任务来自招聘文本、职业标准、企业访谈或专家维护。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>85</x:v>
+        <x:v>招聘文本+职业标准</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>岗位画像算法/人工维护</x:v>
+        <x:v>多来源</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>按版本</x:v>
+        <x:v>按批次</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str"/>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="12" t="str">
-        <x:v>weight</x:v>
-      </x:c>
-      <x:c r="B9" s="11" t="str">
-        <x:v>能力权重</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="str"/>
-      <x:c r="F9" s="11" t="str">
-        <x:v>适岗度或课程映射中的权重。</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="str">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="H9" s="11" t="str">
-        <x:v>专家维护/规则</x:v>
-      </x:c>
-      <x:c r="I9" s="11" t="str">
-        <x:v>按版本</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="str"/>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="12" t="str">
-        <x:v>source_terms</x:v>
-      </x:c>
-      <x:c r="B10" s="11" t="str">
-        <x:v>原始关键词</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="str"/>
-      <x:c r="F10" s="11" t="str">
-        <x:v>招聘文本中映射到该能力的原始词。</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="str">
-        <x:v>Revit建模、碰撞检查、BIM协同</x:v>
-      </x:c>
-      <x:c r="H10" s="11" t="str">
-        <x:v>招聘信息库</x:v>
-      </x:c>
-      <x:c r="I10" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-      <x:c r="J10" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -784,10 +728,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>company_id</x:v>
+        <x:v>ability_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>企业ID</x:v>
+        <x:v>能力项ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>string</x:v>
@@ -799,13 +743,13 @@
         <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>企业主键。</x:v>
+        <x:v>能力项主键。</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>company_glodon</x:v>
+        <x:v>ability_bim_model</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>系统生成/统一社会信用代码</x:v>
+        <x:v>系统生成/模板导入</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
         <x:v>创建时</x:v>
@@ -814,10 +758,10 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>company_name</x:v>
+        <x:v>job_id</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>企业简称</x:v>
+        <x:v>岗位ID</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>string</x:v>
@@ -826,28 +770,30 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>IDX</x:v>
+        <x:v>FK</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>页面展示名称。</x:v>
+        <x:v>所属岗位。</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>广联达</x:v>
+        <x:v>job_bim_deepening</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>企业公开信息/人工维护</x:v>
+        <x:v>岗位库</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-      <x:c r="J3" s="11" t="str"/>
+        <x:v>按项目维护</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="str">
+        <x:v>关联06_岗位库</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>full_name</x:v>
+        <x:v>ability_name</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>企业全称</x:v>
+        <x:v>能力项名称</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>string</x:v>
@@ -856,102 +802,104 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>UK</x:v>
+        <x:v>IDX</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>工商登记或公告中的企业全称。</x:v>
+        <x:v>能力项标准名称，同岗位下不重复。</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>广联达科技股份有限公司</x:v>
+        <x:v>BIM模型深化能力</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>国家企业信用信息公示系统/公告</x:v>
+        <x:v>岗位画像/能力模板</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>按批次</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>credit_code</x:v>
+        <x:v>ability_category</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>统一社会信用代码</x:v>
+        <x:v>能力类别</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>UK</x:v>
+        <x:v>IDX</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>企业唯一信用代码。</x:v>
+        <x:v>知识、技能、素养。</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>91110000700000000X</x:v>
+        <x:v>技能</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>国家企业信用信息公示系统</x:v>
+        <x:v>岗位中心</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>按批次</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str"/>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
+    <x:row r="6" ht="24" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>registration_address</x:v>
+        <x:v>definition</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>注册地址</x:v>
+        <x:v>能力定义</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str">
-        <x:v>工商登记地址。</x:v>
+        <x:v>能力项内涵和边界。</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>北京市海淀区...</x:v>
+        <x:v>能够基于专业软件完成模型深化与构件信息维护</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>国家企业信用信息公示系统</x:v>
+        <x:v>专家维护/AI生成后审核</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>按批次</x:v>
+        <x:v>按版本</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>business_scope</x:v>
+        <x:v>normalized_name</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>经营范围</x:v>
+        <x:v>标准化名称</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="str"/>
+      <x:c r="E7" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>工商登记经营范围。</x:v>
+        <x:v>用于与招聘技能热度、课程能力映射的统一名称。</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>技术开发、软件服务...</x:v>
+        <x:v>BIM深化设计</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>国家企业信用信息公示系统</x:v>
+        <x:v>规则归一/人工复核</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
         <x:v>按批次</x:v>
@@ -960,267 +908,87 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>industry_code</x:v>
+        <x:v>score</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>所属行业代码</x:v>
+        <x:v>能力强度</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str">
-        <x:v>国民经济行业分类代码。</x:v>
+        <x:v>岗位画像或雷达图使用的能力强度。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>I65</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>行业库/规则映射</x:v>
+        <x:v>岗位画像算法/人工维护</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="str">
-        <x:v>关联02_行业库</x:v>
-      </x:c>
+        <x:v>按版本</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="12" t="str">
-        <x:v>industry_name</x:v>
+        <x:v>weight</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>所属行业</x:v>
+        <x:v>能力权重</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+      <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str">
-        <x:v>所属行业展示名称。</x:v>
+        <x:v>适岗度或课程映射中的权重。</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>软件和信息技术服务业</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>行业库/公告</x:v>
+        <x:v>专家维护/规则</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
-        <x:v>按批次</x:v>
+        <x:v>按版本</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="12" t="str">
-        <x:v>location</x:v>
+        <x:v>source_terms</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>地区</x:v>
+        <x:v>原始关键词</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+      <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str">
-        <x:v>企业所在省市区。</x:v>
+        <x:v>招聘文本中映射到该能力的原始词。</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>北京海淀</x:v>
+        <x:v>Revit建模、碰撞检查、BIM协同</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>工商信息/招聘信息</x:v>
+        <x:v>招聘信息库</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
         <x:v>按批次</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="12" t="str">
-        <x:v>tags</x:v>
-      </x:c>
-      <x:c r="B11" s="11" t="str">
-        <x:v>企业标签</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="D11" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
-      <x:c r="F11" s="11" t="str">
-        <x:v>上市、专精特新、龙头企业、校企合作等标签。</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="str">
-        <x:v>上市公司、建筑数字化</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="str">
-        <x:v>公告/政策名单/人工维护</x:v>
-      </x:c>
-      <x:c r="I11" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-      <x:c r="J11" s="11" t="str"/>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="12" t="str">
-        <x:v>products</x:v>
-      </x:c>
-      <x:c r="B12" s="11" t="str">
-        <x:v>核心产品</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="D12" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="str"/>
-      <x:c r="F12" s="11" t="str">
-        <x:v>企业主要产品或服务。</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="str">
-        <x:v>BIM算量平台、智慧工地平台</x:v>
-      </x:c>
-      <x:c r="H12" s="11" t="str">
-        <x:v>企业官网/公告</x:v>
-      </x:c>
-      <x:c r="I12" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-      <x:c r="J12" s="11" t="str"/>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="12" t="str">
-        <x:v>directions</x:v>
-      </x:c>
-      <x:c r="B13" s="11" t="str">
-        <x:v>技术方向</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="D13" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="str"/>
-      <x:c r="F13" s="11" t="str">
-        <x:v>与专业建设相关技术方向。</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="str">
-        <x:v>BIM、工程数字化、AI审图</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="str">
-        <x:v>企业官网/招聘文本</x:v>
-      </x:c>
-      <x:c r="I13" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-      <x:c r="J13" s="11" t="str"/>
-    </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="12" t="str">
-        <x:v>jobs</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="str">
-        <x:v>主要招聘岗位</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="D14" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="str"/>
-      <x:c r="F14" s="11" t="str">
-        <x:v>企业相关岗位。</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="str">
-        <x:v>BIM实施顾问、平台实施工程师</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="str">
-        <x:v>招聘信息库</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="str">
-        <x:v>可拆企业-岗位关系表</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="12" t="str">
-        <x:v>cooperation</x:v>
-      </x:c>
-      <x:c r="B15" s="11" t="str">
-        <x:v>校企合作记录</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="D15" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="str"/>
-      <x:c r="F15" s="11" t="str">
-        <x:v>合作基地、订单班、实训项目等。</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="str">
-        <x:v>产业学院共建</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="str">
-        <x:v>学校资料/CMS</x:v>
-      </x:c>
-      <x:c r="I15" s="11" t="str">
-        <x:v>按项目维护</x:v>
-      </x:c>
-      <x:c r="J15" s="11" t="str"/>
-    </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="12" t="str">
-        <x:v>source_url</x:v>
-      </x:c>
-      <x:c r="B16" s="11" t="str">
-        <x:v>来源链接</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="str">
-        <x:v>url</x:v>
-      </x:c>
-      <x:c r="D16" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="str"/>
-      <x:c r="F16" s="11" t="str">
-        <x:v>企业工商、公告或官网来源。</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="str">
-        <x:v>https://www.gsxt.gov.cn/</x:v>
-      </x:c>
-      <x:c r="H16" s="11" t="str">
-        <x:v>数据来源库</x:v>
-      </x:c>
-      <x:c r="I16" s="11" t="str">
-        <x:v>随采集</x:v>
-      </x:c>
-      <x:c r="J16" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1277,10 +1045,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>posting_id</x:v>
+        <x:v>company_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>招聘信息ID</x:v>
+        <x:v>企业ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>string</x:v>
@@ -1292,25 +1060,25 @@
         <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>单条招聘信息主键，建议按来源平台+原始ID生成。</x:v>
+        <x:v>企业主键。</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>zhaopin_123456</x:v>
+        <x:v>company_glodon</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>采集任务</x:v>
+        <x:v>系统生成/统一社会信用代码</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
-        <x:v>采集时</x:v>
+        <x:v>创建时</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>source_platform</x:v>
+        <x:v>company_name</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>来源平台</x:v>
+        <x:v>企业简称</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>string</x:v>
@@ -1322,179 +1090,173 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>招聘信息来源平台。</x:v>
+        <x:v>页面展示名称。</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>中国公共招聘网</x:v>
+        <x:v>广联达</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>采集任务</x:v>
+        <x:v>企业公开信息/人工维护</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>采集时</x:v>
+        <x:v>按批次</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>source_url</x:v>
+        <x:v>full_name</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>原文链接</x:v>
+        <x:v>企业全称</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>url</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>IDX</x:v>
+        <x:v>UK</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>招聘详情页URL。</x:v>
+        <x:v>工商登记或公告中的企业全称。</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>https://job.mohrss.gov.cn/...</x:v>
+        <x:v>广联达科技股份有限公司</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>采集任务</x:v>
+        <x:v>国家企业信用信息公示系统/公告</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>采集时</x:v>
+        <x:v>按批次</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>job_title</x:v>
+        <x:v>credit_code</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>招聘标题</x:v>
+        <x:v>统一社会信用代码</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>IDX</x:v>
+        <x:v>UK</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>原始招聘标题。</x:v>
+        <x:v>企业唯一信用代码。</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>BIM深化设计工程师</x:v>
+        <x:v>91110000700000000X</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>招聘平台</x:v>
+        <x:v>国家企业信用信息公示系统</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>高频</x:v>
+        <x:v>按批次</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>normalized_job_id</x:v>
+        <x:v>registration_address</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>归一岗位ID</x:v>
+        <x:v>注册地址</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str">
-        <x:v>归一到平台岗位库的岗位ID。</x:v>
+        <x:v>工商登记地址。</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>job_bim_deepening</x:v>
+        <x:v>北京市海淀区...</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>岗位归一规则/人工复核</x:v>
+        <x:v>国家企业信用信息公示系统</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
         <x:v>按批次</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="str">
-        <x:v>关联06_岗位库</x:v>
-      </x:c>
+      <x:c r="J6" s="11" t="str"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>company_id</x:v>
+        <x:v>business_scope</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>企业ID</x:v>
+        <x:v>经营范围</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str">
-        <x:v>匹配到企业库的企业ID。</x:v>
+        <x:v>工商登记经营范围。</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>company_glodon</x:v>
+        <x:v>技术开发、软件服务...</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>企业归一规则</x:v>
+        <x:v>国家企业信用信息公示系统</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
         <x:v>按批次</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="str">
-        <x:v>关联09_企业库</x:v>
-      </x:c>
+      <x:c r="J7" s="11" t="str"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>company_name_raw</x:v>
+        <x:v>industry_code</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>原始企业名称</x:v>
+        <x:v>所属行业代码</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>IDX</x:v>
+        <x:v>FK</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>招聘平台展示的企业名称。</x:v>
+        <x:v>国民经济行业分类代码。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>广联达科技股份有限公司</x:v>
+        <x:v>I65</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>招聘平台</x:v>
+        <x:v>行业库/规则映射</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="str"/>
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str">
+        <x:v>关联02_行业库</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="12" t="str">
-        <x:v>city</x:v>
+        <x:v>industry_name</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>城市</x:v>
+        <x:v>所属行业</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>string</x:v>
@@ -1506,368 +1268,220 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>岗位所在城市。</x:v>
+        <x:v>所属行业展示名称。</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>北京</x:v>
+        <x:v>软件和信息技术服务业</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>招聘平台</x:v>
+        <x:v>行业库/公告</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
-        <x:v>高频</x:v>
+        <x:v>按批次</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="12" t="str">
-        <x:v>salary_min</x:v>
+        <x:v>location</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>最低薪资</x:v>
+        <x:v>地区</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="str"/>
+      <x:c r="E10" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>解析后的最低月薪，单位元。</x:v>
+        <x:v>企业所在省市区。</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>10000</x:v>
+        <x:v>北京海淀</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>招聘文本解析</x:v>
+        <x:v>工商信息/招聘信息</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
-        <x:v>高频</x:v>
+        <x:v>按批次</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="12" t="str">
-        <x:v>salary_max</x:v>
+        <x:v>tags</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>最高薪资</x:v>
+        <x:v>企业标签</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="str"/>
+      <x:c r="E11" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>解析后的最高月薪，单位元。</x:v>
+        <x:v>上市、专精特新、龙头企业、校企合作等标签。</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>18000</x:v>
+        <x:v>上市公司、建筑数字化</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>招聘文本解析</x:v>
+        <x:v>公告/政策名单/人工维护</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
-        <x:v>高频</x:v>
+        <x:v>按批次</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="12" t="str">
-        <x:v>salary_text</x:v>
+        <x:v>products</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>薪资原文</x:v>
+        <x:v>核心产品</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str">
-        <x:v>招聘平台原始薪资字段。</x:v>
+        <x:v>企业主要产品或服务。</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>10K-18K</x:v>
+        <x:v>BIM算量平台、智慧工地平台</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
-        <x:v>招聘平台</x:v>
+        <x:v>企业官网/公告</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
-        <x:v>高频</x:v>
+        <x:v>按批次</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="12" t="str">
-        <x:v>education</x:v>
+        <x:v>directions</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>学历要求</x:v>
+        <x:v>技术方向</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+      <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str">
-        <x:v>原始或归一学历要求。</x:v>
+        <x:v>与专业建设相关技术方向。</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>大专及以上</x:v>
+        <x:v>BIM、工程数字化、AI审图</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str">
-        <x:v>招聘平台/规则归一</x:v>
+        <x:v>企业官网/招聘文本</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str">
-        <x:v>高频</x:v>
+        <x:v>按批次</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="12" t="str">
-        <x:v>experience</x:v>
+        <x:v>jobs</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>经验要求</x:v>
+        <x:v>主要招聘岗位</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+      <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str">
-        <x:v>原始或归一经验要求。</x:v>
+        <x:v>企业相关岗位。</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>1-3年</x:v>
+        <x:v>BIM实施顾问、平台实施工程师</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str">
-        <x:v>招聘平台/规则归一</x:v>
+        <x:v>招聘信息库</x:v>
       </x:c>
       <x:c r="I14" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="str"/>
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="str">
+        <x:v>可拆企业-岗位关系表</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="12" t="str">
-        <x:v>headcount</x:v>
+        <x:v>cooperation</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>招聘人数</x:v>
+        <x:v>校企合作记录</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str">
-        <x:v>招聘人数，缺失时为空。</x:v>
+        <x:v>合作基地、订单班、实训项目等。</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>3</x:v>
+        <x:v>产业学院共建</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
-        <x:v>招聘平台</x:v>
+        <x:v>学校资料/CMS</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str">
-        <x:v>高频</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str"/>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="12" t="str">
-        <x:v>job_description</x:v>
+        <x:v>source_url</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
-        <x:v>岗位职责</x:v>
+        <x:v>来源链接</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>url</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str">
-        <x:v>招聘正文职责描述。</x:v>
+        <x:v>企业工商、公告或官网来源。</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>负责BIM模型深化...</x:v>
+        <x:v>https://www.gsxt.gov.cn/</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str">
-        <x:v>招聘平台</x:v>
+        <x:v>数据来源库</x:v>
       </x:c>
       <x:c r="I16" s="11" t="str">
-        <x:v>高频</x:v>
+        <x:v>随采集</x:v>
       </x:c>
       <x:c r="J16" s="11" t="str"/>
-    </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="12" t="str">
-        <x:v>requirements</x:v>
-      </x:c>
-      <x:c r="B17" s="11" t="str">
-        <x:v>任职要求</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="D17" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="str"/>
-      <x:c r="F17" s="11" t="str">
-        <x:v>招聘正文任职要求。</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="str">
-        <x:v>熟悉Revit/Navisworks...</x:v>
-      </x:c>
-      <x:c r="H17" s="11" t="str">
-        <x:v>招聘平台</x:v>
-      </x:c>
-      <x:c r="I17" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-      <x:c r="J17" s="11" t="str"/>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="12" t="str">
-        <x:v>skill_terms</x:v>
-      </x:c>
-      <x:c r="B18" s="11" t="str">
-        <x:v>技能关键词</x:v>
-      </x:c>
-      <x:c r="C18" s="11" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="D18" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
-      <x:c r="F18" s="11" t="str">
-        <x:v>从职责和要求中抽取的技能词。</x:v>
-      </x:c>
-      <x:c r="G18" s="11" t="str">
-        <x:v>Revit,Navisworks,BIM协同</x:v>
-      </x:c>
-      <x:c r="H18" s="11" t="str">
-        <x:v>NLP抽取/规则</x:v>
-      </x:c>
-      <x:c r="I18" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-      <x:c r="J18" s="11" t="str">
-        <x:v>关联08_岗位能力库</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="12" t="str">
-        <x:v>publish_date</x:v>
-      </x:c>
-      <x:c r="B19" s="11" t="str">
-        <x:v>发布时间</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="str">
-        <x:v>date</x:v>
-      </x:c>
-      <x:c r="D19" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="str">
-        <x:v>招聘信息发布时间。</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="str">
-        <x:v>2026-06-01</x:v>
-      </x:c>
-      <x:c r="H19" s="11" t="str">
-        <x:v>招聘平台</x:v>
-      </x:c>
-      <x:c r="I19" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-      <x:c r="J19" s="11" t="str"/>
-    </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="12" t="str">
-        <x:v>crawl_time</x:v>
-      </x:c>
-      <x:c r="B20" s="11" t="str">
-        <x:v>采集时间</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="str">
-        <x:v>datetime</x:v>
-      </x:c>
-      <x:c r="D20" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="str">
-        <x:v>采集任务实际采集时间。</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="str">
-        <x:v>2026-06-22 10:00</x:v>
-      </x:c>
-      <x:c r="H20" s="11" t="str">
-        <x:v>采集任务</x:v>
-      </x:c>
-      <x:c r="I20" s="11" t="str">
-        <x:v>每次采集</x:v>
-      </x:c>
-      <x:c r="J20" s="11" t="str"/>
-    </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="12" t="str">
-        <x:v>batch_id</x:v>
-      </x:c>
-      <x:c r="B21" s="11" t="str">
-        <x:v>采集批次ID</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D21" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="str">
-        <x:v>归属采集批次。</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="str">
-        <x:v>batch_job_20260622</x:v>
-      </x:c>
-      <x:c r="H21" s="11" t="str">
-        <x:v>采集任务</x:v>
-      </x:c>
-      <x:c r="I21" s="11" t="str">
-        <x:v>每次采集</x:v>
-      </x:c>
-      <x:c r="J21" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1924,10 +1538,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>trend_id</x:v>
+        <x:v>posting_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>趋势记录ID</x:v>
+        <x:v>招聘信息ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>string</x:v>
@@ -1939,25 +1553,25 @@
         <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>统计周期下趋势记录主键。</x:v>
+        <x:v>单条招聘信息主键，建议按来源平台+原始ID生成。</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>trend_202606_smart_construction</x:v>
+        <x:v>zhaopin_123456</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>系统生成</x:v>
+        <x:v>采集任务</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
-        <x:v>每次计算</x:v>
+        <x:v>采集时</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>period</x:v>
+        <x:v>source_platform</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>统计周期</x:v>
+        <x:v>来源平台</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>string</x:v>
@@ -1969,57 +1583,55 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>统计月份、季度或滚动周期。</x:v>
+        <x:v>招聘信息来源平台。</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>2026-06</x:v>
+        <x:v>中国公共招聘网</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>统计任务</x:v>
+        <x:v>采集任务</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>采集时</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>major_id</x:v>
+        <x:v>source_url</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>专业ID</x:v>
+        <x:v>原文链接</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>url</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>FK</x:v>
+        <x:v>IDX</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>趋势关联专业。</x:v>
+        <x:v>招聘详情页URL。</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>maj_460301</x:v>
+        <x:v>https://job.mohrss.gov.cn/...</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>专业库</x:v>
+        <x:v>采集任务</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>月度</x:v>
-      </x:c>
-      <x:c r="J4" s="11" t="str">
-        <x:v>关联01_专业库</x:v>
-      </x:c>
+        <x:v>采集时</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>chain_id</x:v>
+        <x:v>job_title</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>产业链ID</x:v>
+        <x:v>招聘标题</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>string</x:v>
@@ -2028,28 +1640,28 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>FK</x:v>
+        <x:v>IDX</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>趋势对应产业链。</x:v>
+        <x:v>原始招聘标题。</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>chain_smart_construction</x:v>
+        <x:v>BIM深化设计工程师</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>产业链库</x:v>
+        <x:v>招聘平台</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>高频</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>industry_node_id</x:v>
+        <x:v>normalized_job_id</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>产业环节ID</x:v>
+        <x:v>归一岗位ID</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>string</x:v>
@@ -2061,25 +1673,27 @@
         <x:v>FK</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>可按产业环节统计。</x:v>
+        <x:v>归一到平台岗位库的岗位ID。</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>node_bim_platform</x:v>
+        <x:v>job_bim_deepening</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>产业环节库</x:v>
+        <x:v>岗位归一规则/人工复核</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>月度</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="str"/>
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
+        <x:v>关联06_岗位库</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>job_id</x:v>
+        <x:v>company_id</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>岗位ID</x:v>
+        <x:v>企业ID</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>string</x:v>
@@ -2091,83 +1705,87 @@
         <x:v>FK</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>可按岗位统计。</x:v>
+        <x:v>匹配到企业库的企业ID。</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>job_bim_deepening</x:v>
+        <x:v>company_glodon</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>岗位库</x:v>
+        <x:v>企业归一规则</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>月度</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="str"/>
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str">
+        <x:v>关联09_企业库</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>city</x:v>
+        <x:v>company_name_raw</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>城市</x:v>
+        <x:v>原始企业名称</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>可按城市统计。</x:v>
+        <x:v>招聘平台展示的企业名称。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>杭州</x:v>
+        <x:v>广联达科技股份有限公司</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>招聘信息库</x:v>
+        <x:v>招聘平台</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>高频</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="12" t="str">
-        <x:v>total_demand</x:v>
+        <x:v>city</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>招聘总量</x:v>
+        <x:v>城市</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="str"/>
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>周期内招聘信息数量或折算需求量。</x:v>
+        <x:v>岗位所在城市。</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2176</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>招聘信息库聚合</x:v>
+        <x:v>招聘平台</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>高频</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="12" t="str">
-        <x:v>avg_salary</x:v>
+        <x:v>salary_min</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>平均薪资</x:v>
+        <x:v>最低薪资</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>number</x:v>
@@ -2177,25 +1795,25 @@
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str">
-        <x:v>周期内薪资均值，单位元/月。</x:v>
+        <x:v>解析后的最低月薪，单位元。</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>14500</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>招聘信息库聚合</x:v>
+        <x:v>招聘文本解析</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>高频</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="12" t="str">
-        <x:v>company_sample_count</x:v>
+        <x:v>salary_max</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>企业样本数</x:v>
+        <x:v>最高薪资</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>number</x:v>
@@ -2205,130 +1823,312 @@
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str">
-        <x:v>参与统计的企业去重数量。</x:v>
+        <x:v>解析后的最高月薪，单位元。</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>326</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>招聘信息库聚合</x:v>
+        <x:v>招聘文本解析</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>高频</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
     </x:row>
-    <x:row r="12" ht="24" hidden="0" customHeight="1">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="12" t="str">
-        <x:v>high_frequency_job_count</x:v>
+        <x:v>salary_text</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>高频岗位数</x:v>
+        <x:v>薪资原文</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str">
-        <x:v>达到阈值的岗位数量。</x:v>
+        <x:v>招聘平台原始薪资字段。</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>12</x:v>
+        <x:v>10K-18K</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
-        <x:v>统计规则</x:v>
+        <x:v>招聘平台</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>高频</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="12" t="str">
-        <x:v>growth_rate</x:v>
+        <x:v>education</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>增长率</x:v>
+        <x:v>学历要求</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="str"/>
+      <x:c r="E13" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
       <x:c r="F13" s="11" t="str">
-        <x:v>同比或环比增长率。</x:v>
+        <x:v>原始或归一学历要求。</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>0.128</x:v>
+        <x:v>大专及以上</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str">
-        <x:v>统计任务</x:v>
+        <x:v>招聘平台/规则归一</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>高频</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="12" t="str">
-        <x:v>top_skill_terms</x:v>
+        <x:v>experience</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>高频技能</x:v>
+        <x:v>经验要求</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="str"/>
+      <x:c r="E14" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
       <x:c r="F14" s="11" t="str">
-        <x:v>周期内高频技能词。</x:v>
+        <x:v>原始或归一经验要求。</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>BIM协同、模型深化、智慧工地</x:v>
+        <x:v>1-3年</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str">
-        <x:v>招聘信息库聚合</x:v>
+        <x:v>招聘平台/规则归一</x:v>
       </x:c>
       <x:c r="I14" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>高频</x:v>
       </x:c>
       <x:c r="J14" s="11" t="str"/>
     </x:row>
-    <x:row r="15" ht="24" hidden="0" customHeight="1">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="12" t="str">
-        <x:v>source_batch_ids</x:v>
+        <x:v>headcount</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>来源批次</x:v>
+        <x:v>招聘人数</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str">
-        <x:v>参与统计的采集批次。</x:v>
+        <x:v>招聘人数，缺失时为空。</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>batch_job_20260601,batch_job_20260622</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
-        <x:v>采集批次库</x:v>
+        <x:v>招聘平台</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>高频</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str"/>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="12" t="str">
+        <x:v>job_description</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
+        <x:v>岗位职责</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str"/>
+      <x:c r="F16" s="11" t="str">
+        <x:v>招聘正文职责描述。</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="str">
+        <x:v>负责BIM模型深化...</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="str">
+        <x:v>招聘平台</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="str">
+        <x:v>高频</x:v>
+      </x:c>
+      <x:c r="J16" s="11" t="str"/>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="12" t="str">
+        <x:v>requirements</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="str">
+        <x:v>任职要求</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str"/>
+      <x:c r="F17" s="11" t="str">
+        <x:v>招聘正文任职要求。</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="str">
+        <x:v>熟悉Revit/Navisworks...</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="str">
+        <x:v>招聘平台</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="str">
+        <x:v>高频</x:v>
+      </x:c>
+      <x:c r="J17" s="11" t="str"/>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="12" t="str">
+        <x:v>skill_terms</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="str">
+        <x:v>技能关键词</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="str">
+        <x:v>从职责和要求中抽取的技能词。</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="str">
+        <x:v>Revit,Navisworks,BIM协同</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="str">
+        <x:v>NLP抽取/规则</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="str">
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J18" s="11" t="str">
+        <x:v>关联08_岗位能力库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="12" t="str">
+        <x:v>publish_date</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="str">
+        <x:v>发布时间</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="str">
+        <x:v>date</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="str">
+        <x:v>招聘信息发布时间。</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="str">
+        <x:v>2026-06-01</x:v>
+      </x:c>
+      <x:c r="H19" s="11" t="str">
+        <x:v>招聘平台</x:v>
+      </x:c>
+      <x:c r="I19" s="11" t="str">
+        <x:v>高频</x:v>
+      </x:c>
+      <x:c r="J19" s="11" t="str"/>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="12" t="str">
+        <x:v>crawl_time</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="str">
+        <x:v>采集时间</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="str">
+        <x:v>datetime</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="str">
+        <x:v>采集任务实际采集时间。</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="str">
+        <x:v>2026-06-22 10:00</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="str">
+        <x:v>采集任务</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="str">
+        <x:v>每次采集</x:v>
+      </x:c>
+      <x:c r="J20" s="11" t="str"/>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="12" t="str">
+        <x:v>batch_id</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="str">
+        <x:v>采集批次ID</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="str">
+        <x:v>归属采集批次。</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="str">
+        <x:v>batch_job_20260622</x:v>
+      </x:c>
+      <x:c r="H21" s="11" t="str">
+        <x:v>采集任务</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="str">
+        <x:v>每次采集</x:v>
+      </x:c>
+      <x:c r="J21" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2385,10 +2185,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>competition_id</x:v>
+        <x:v>trend_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>赛事ID</x:v>
+        <x:v>趋势记录ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>string</x:v>
@@ -2400,25 +2200,25 @@
         <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>赛事主键。</x:v>
+        <x:v>统计周期下趋势记录主键。</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>comp_vscc_bim_2026</x:v>
+        <x:v>trend_202606_smart_construction</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>系统生成/赛事采集</x:v>
+        <x:v>系统生成</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
-        <x:v>创建时</x:v>
+        <x:v>每次计算</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>competition_name</x:v>
+        <x:v>period</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>赛事名称</x:v>
+        <x:v>统计周期</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>string</x:v>
@@ -2430,83 +2230,87 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>赛事或赛项名称。</x:v>
+        <x:v>统计月份、季度或滚动周期。</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>建筑信息模型建模与应用</x:v>
+        <x:v>2026-06</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>赛事官网</x:v>
+        <x:v>统计任务</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>按赛事年度</x:v>
+        <x:v>月度</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>competition_level</x:v>
+        <x:v>major_id</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>赛事级别</x:v>
+        <x:v>专业ID</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>IDX</x:v>
+        <x:v>FK</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>国家级、国际级、省级、行业级、校级。</x:v>
+        <x:v>趋势关联专业。</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>国家级</x:v>
+        <x:v>maj_460301</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>赛事官网/政策文件</x:v>
+        <x:v>专业库</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>按赛事年度</x:v>
-      </x:c>
-      <x:c r="J4" s="11" t="str"/>
+        <x:v>月度</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str">
+        <x:v>关联01_专业库</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>organizer</x:v>
+        <x:v>chain_id</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>主办单位</x:v>
+        <x:v>产业链ID</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="str"/>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>FK</x:v>
+      </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>赛事主办或承办单位。</x:v>
+        <x:v>趋势对应产业链。</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>教育部等</x:v>
+        <x:v>chain_smart_construction</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>赛事官网/通知</x:v>
+        <x:v>产业链库</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>按赛事年度</x:v>
+        <x:v>月度</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>event_category</x:v>
+        <x:v>industry_node_id</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>赛项类别</x:v>
+        <x:v>产业环节ID</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>string</x:v>
@@ -2515,191 +2319,277 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>IDX</x:v>
+        <x:v>FK</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>技能竞赛、创新创业竞赛、行业赛项等。</x:v>
+        <x:v>可按产业环节统计。</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>职业院校技能竞赛</x:v>
+        <x:v>node_bim_platform</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>赛事官网</x:v>
+        <x:v>产业环节库</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>按赛事年度</x:v>
+        <x:v>月度</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>major_codes</x:v>
+        <x:v>job_id</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>适配专业</x:v>
+        <x:v>岗位ID</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="str"/>
+      <x:c r="E7" s="11" t="str">
+        <x:v>FK</x:v>
+      </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>赛项可关联专业代码。</x:v>
+        <x:v>可按岗位统计。</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>440301,440305</x:v>
+        <x:v>job_bim_deepening</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>赛项规程/人工维护</x:v>
+        <x:v>岗位库</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>按赛事年度</x:v>
+        <x:v>月度</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>ability_requirements</x:v>
+        <x:v>city</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>能力要求</x:v>
+        <x:v>城市</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="str"/>
+      <x:c r="E8" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>赛项考查能力。</x:v>
+        <x:v>可按城市统计。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>模型建立、协同应用、成果表达</x:v>
+        <x:v>杭州</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>赛项规程</x:v>
+        <x:v>招聘信息库</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>按赛事年度</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="str">
-        <x:v>关联08_岗位能力库</x:v>
-      </x:c>
+        <x:v>月度</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="12" t="str">
-        <x:v>competition_rules_url</x:v>
+        <x:v>total_demand</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>赛项规程链接</x:v>
+        <x:v>招聘总量</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>url</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str">
-        <x:v>赛项规程、通知或指南链接。</x:v>
+        <x:v>周期内招聘信息数量或折算需求量。</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>https://www.chinaskills-jsw.org/</x:v>
+        <x:v>2176</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>赛事官网</x:v>
+        <x:v>招聘信息库聚合</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
-        <x:v>随采集</x:v>
+        <x:v>月度</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="12" t="str">
-        <x:v>award_info</x:v>
+        <x:v>avg_salary</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>获奖信息</x:v>
+        <x:v>平均薪资</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str">
-        <x:v>获奖等级、团队、学校等。</x:v>
+        <x:v>周期内薪资均值，单位元/月。</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>一等奖</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>赛事官网/学校资料</x:v>
+        <x:v>招聘信息库聚合</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
-        <x:v>按赛事年度</x:v>
+        <x:v>月度</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="12" t="str">
-        <x:v>result_transform</x:v>
+        <x:v>company_sample_count</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>成果转化方向</x:v>
+        <x:v>企业样本数</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str">
-        <x:v>赛项成果与课程、实训、证书的转化。</x:v>
+        <x:v>参与统计的企业去重数量。</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>转化为BIM综合实训项目</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>人工维护</x:v>
+        <x:v>招聘信息库聚合</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
-        <x:v>按项目维护</x:v>
+        <x:v>月度</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
     </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
+    <x:row r="12" ht="24" hidden="0" customHeight="1">
       <x:c r="A12" s="12" t="str">
-        <x:v>source_url</x:v>
+        <x:v>high_frequency_job_count</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>来源链接</x:v>
+        <x:v>高频岗位数</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>url</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str">
-        <x:v>赛事来源URL。</x:v>
+        <x:v>达到阈值的岗位数量。</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>https://www.chinaskills-jsw.org/</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
-        <x:v>数据来源库</x:v>
+        <x:v>统计规则</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
-        <x:v>随采集</x:v>
+        <x:v>月度</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="12" t="str">
+        <x:v>growth_rate</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>增长率</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str"/>
+      <x:c r="F13" s="11" t="str">
+        <x:v>同比或环比增长率。</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str">
+        <x:v>0.128</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str">
+        <x:v>统计任务</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str">
+        <x:v>月度</x:v>
+      </x:c>
+      <x:c r="J13" s="11" t="str"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="12" t="str">
+        <x:v>top_skill_terms</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>高频技能</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str"/>
+      <x:c r="F14" s="11" t="str">
+        <x:v>周期内高频技能词。</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="str">
+        <x:v>BIM协同、模型深化、智慧工地</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="str">
+        <x:v>招聘信息库聚合</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="str">
+        <x:v>月度</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="str"/>
+    </x:row>
+    <x:row r="15" ht="24" hidden="0" customHeight="1">
+      <x:c r="A15" s="12" t="str">
+        <x:v>source_batch_ids</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="str">
+        <x:v>来源批次</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str"/>
+      <x:c r="F15" s="11" t="str">
+        <x:v>参与统计的采集批次。</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="str">
+        <x:v>batch_job_20260601,batch_job_20260622</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="str">
+        <x:v>采集批次库</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="str">
+        <x:v>月度</x:v>
+      </x:c>
+      <x:c r="J15" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2756,10 +2646,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>certificate_id</x:v>
+        <x:v>tech_match_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>证书ID</x:v>
+        <x:v>新技术匹配ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>string</x:v>
@@ -2771,25 +2661,25 @@
         <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>证书主键。</x:v>
+        <x:v>新技术方向、岗位、专业和课程建议的一条匹配记录。</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>cert_bim_middle</x:v>
+        <x:v>techmatch_robot_bim_001</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>系统生成/证书采集</x:v>
+        <x:v>系统生成/AI生成后审核</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
-        <x:v>创建时</x:v>
+        <x:v>每次研判</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>certificate_name</x:v>
+        <x:v>technology_name</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>证书名称</x:v>
+        <x:v>技术方向名称</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>string</x:v>
@@ -2801,115 +2691,115 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>证书标准名称。</x:v>
+        <x:v>新岗位新技术页面展示的技术方向。</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>建筑信息模型职业技能等级证书</x:v>
+        <x:v>BIM+数字孪生工地</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>证书平台/职业资格目录</x:v>
+        <x:v>产业资料/招聘趋势/AI生成后审核</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>按官方更新</x:v>
+        <x:v>按版本</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>certificate_type</x:v>
+        <x:v>maturity_stage</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>证书类型</x:v>
+        <x:v>成熟阶段</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>enum</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>职业资格、职业技能等级、1+X、行业证书等。</x:v>
+        <x:v>导入期、成长期、应用扩散期、成熟期或待评估。</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>职业技能等级证书</x:v>
+        <x:v>应用扩散期</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>证书平台</x:v>
+        <x:v>产业研究/专家复核</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>按官方更新</x:v>
+        <x:v>按版本</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
     </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
+    <x:row r="5" ht="24" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>level</x:v>
+        <x:v>impact_summary</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>证书等级</x:v>
+        <x:v>产业影响</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E5" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+      <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str">
-        <x:v>初级、中级、高级或专项。</x:v>
+        <x:v>该技术对产业环节、岗位需求和课程实训的影响摘要。</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>中级</x:v>
+        <x:v>推动施工现场数据采集、模型联动和运维交付能力升级</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>证书平台</x:v>
+        <x:v>产业研究/AI生成后审核</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>按官方更新</x:v>
+        <x:v>按版本</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>issuer</x:v>
+        <x:v>chain_id</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>颁发/评价机构</x:v>
+        <x:v>产业链ID</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>IDX</x:v>
+        <x:v>FK</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>证书颁发或评价组织。</x:v>
+        <x:v>技术方向归属或适用的产业链。</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>评价组织名称</x:v>
+        <x:v>chain_smart_construction</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>证书平台/目录</x:v>
+        <x:v>产业链库</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>按官方更新</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="str"/>
+        <x:v>按项目维护</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
+        <x:v>关联03_产业链库</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>occupation_code</x:v>
+        <x:v>industry_node_id</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>对应职业/工种编码</x:v>
+        <x:v>产业环节ID</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>string</x:v>
@@ -2921,55 +2811,59 @@
         <x:v>FK</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>证书对应职业编码或工种编码。</x:v>
+        <x:v>技术方向重点关联的产业环节。</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>4-04-05-04</x:v>
+        <x:v>node_smart_site</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>职业资格目录/职业标准</x:v>
+        <x:v>产业环节库</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>按官方更新</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str">
-        <x:v>关联05_职业库</x:v>
+        <x:v>关联04_产业环节库</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>exam_items</x:v>
+        <x:v>job_id</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>考试科目/考核内容</x:v>
+        <x:v>岗位ID</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="str"/>
+      <x:c r="E8" s="11" t="str">
+        <x:v>FK</x:v>
+      </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>考试科目、技能考核模块。</x:v>
+        <x:v>该技术方向催生或强化的关联岗位。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>理论知识、实操考核</x:v>
+        <x:v>job_digital_twin_engineer</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>证书说明/评价规范</x:v>
+        <x:v>岗位库</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>按官方更新</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="str"/>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str">
+        <x:v>关联06_岗位库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" hidden="0" customHeight="1">
       <x:c r="A9" s="12" t="str">
-        <x:v>requirements</x:v>
+        <x:v>career_path</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>报考条件</x:v>
+        <x:v>职业路径</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>text</x:v>
@@ -2979,53 +2873,57 @@
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str">
-        <x:v>报考条件或适用人群。</x:v>
+        <x:v>关联岗位从初级到高级或管理方向的发展路径，可冗余自岗位库。</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>相关专业在校生或从业人员</x:v>
+        <x:v>BIM建模员 -&gt; 数字孪生实施工程师 -&gt; 智慧工地解决方案经理</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>证书说明/评价规范</x:v>
+        <x:v>岗位库/岗位画像</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
-        <x:v>按官方更新</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="str"/>
+        <x:v>按版本</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str">
+        <x:v>对应06_岗位库.career_path</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="12" t="str">
-        <x:v>valid_period</x:v>
+        <x:v>major_codes</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>有效期</x:v>
+        <x:v>推荐/相关专业</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str">
-        <x:v>证书有效期。</x:v>
+        <x:v>适合协同建设的专业代码列表。</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>长期有效/以官网为准</x:v>
+        <x:v>440301,440304</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>证书说明</x:v>
+        <x:v>专业库/规则匹配/人工复核</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
-        <x:v>按官方更新</x:v>
-      </x:c>
-      <x:c r="J10" s="11" t="str"/>
-    </x:row>
-    <x:row r="11" ht="24" hidden="0" customHeight="1">
+        <x:v>按版本</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="str">
+        <x:v>关联01_专业库.major_code</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="12" t="str">
-        <x:v>fit_job_ids</x:v>
+        <x:v>course_ids</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>适用岗位</x:v>
+        <x:v>建议课程</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>text</x:v>
@@ -3035,25 +2933,27 @@
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str">
-        <x:v>适配岗位ID列表。</x:v>
+        <x:v>建议补强或新增的课程ID列表。</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>job_bim_modeler,job_bim_deepening</x:v>
+        <x:v>course_bim_app,course_iot_site</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>岗位-证书映射</x:v>
+        <x:v>课程库/AI生成后审核</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
-        <x:v>按项目维护</x:v>
-      </x:c>
-      <x:c r="J11" s="11" t="str"/>
+        <x:v>按学年</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="str">
+        <x:v>关联14_课程库</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="12" t="str">
-        <x:v>fit_major_codes</x:v>
+        <x:v>ability_ids</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>适配专业</x:v>
+        <x:v>推荐能力</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>text</x:v>
@@ -3063,46 +2963,226 @@
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str">
-        <x:v>适配专业代码列表。</x:v>
+        <x:v>该技术方向对应的岗位能力项ID列表。</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>440301,440305</x:v>
+        <x:v>ability_bim_model,ability_iot_data</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
-        <x:v>证书说明/人工维护</x:v>
+        <x:v>岗位能力库/规则匹配</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
-        <x:v>按项目维护</x:v>
-      </x:c>
-      <x:c r="J12" s="11" t="str"/>
+        <x:v>按版本</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="str">
+        <x:v>关联08_岗位能力库</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="12" t="str">
-        <x:v>source_url</x:v>
+        <x:v>demand_level</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>来源链接</x:v>
+        <x:v>紧缺度</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>url</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="str">
+        <x:v>根据招聘趋势或专家规则形成的紧缺等级。</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str">
+        <x:v>招聘趋势库/规则</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str">
+        <x:v>月度/批次</x:v>
+      </x:c>
+      <x:c r="J13" s="11" t="str"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="12" t="str">
+        <x:v>salary_range</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>薪资区间</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str"/>
+      <x:c r="F14" s="11" t="str">
+        <x:v>关联新岗位或样本岗位的薪资区间。</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="str">
+        <x:v>12K-20K</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="str">
+        <x:v>岗位库/招聘趋势库</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="str">
+        <x:v>月度/批次</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="str"/>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="12" t="str">
+        <x:v>evidence_source_ids</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="str">
+        <x:v>证据来源</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str"/>
+      <x:c r="F15" s="11" t="str">
+        <x:v>支撑该匹配的招聘批次、政策、产业资料或人工复核记录。</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="str">
+        <x:v>batch_job_202606,policy_miit_001</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="str">
+        <x:v>数据来源库/采集批次</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="str">
+        <x:v>每次研判</x:v>
+      </x:c>
+      <x:c r="J15" s="11" t="str"/>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="12" t="str">
+        <x:v>ai_generated_flag</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
+        <x:v>是否AI生成</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="str"/>
-      <x:c r="F13" s="11" t="str">
-        <x:v>证书查询或目录来源URL。</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="str">
-        <x:v>https://zscx.osta.org.cn/</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="str">
-        <x:v>数据来源库</x:v>
-      </x:c>
-      <x:c r="I13" s="11" t="str">
-        <x:v>随采集</x:v>
-      </x:c>
-      <x:c r="J13" s="11" t="str"/>
+      <x:c r="E16" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="str">
+        <x:v>该记录是否由AI生成或辅助生成。</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="str">
+        <x:v>系统生成</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="str">
+        <x:v>每次研判</x:v>
+      </x:c>
+      <x:c r="J16" s="11" t="str"/>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="12" t="str">
+        <x:v>review_status</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="str">
+        <x:v>审核状态</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="str">
+        <x:v>待审核、已审核、需补充证据、停用。</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="str">
+        <x:v>待审核</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="str">
+        <x:v>运营/专家复核</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="str">
+        <x:v>按版本</x:v>
+      </x:c>
+      <x:c r="J17" s="11" t="str"/>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="12" t="str">
+        <x:v>source_batch_id</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="str">
+        <x:v>来源批次ID</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="str">
+        <x:v>该研判记录归属的初始化或采集批次。</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="str">
+        <x:v>init_20260622_001</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="str">
+        <x:v>初始化批次库</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="str">
+        <x:v>每次研判</x:v>
+      </x:c>
+      <x:c r="J18" s="11" t="str">
+        <x:v>关联16_初始化批次库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="12" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="str">
+        <x:v>datetime</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="str"/>
+      <x:c r="F19" s="11" t="str">
+        <x:v>记录最近生成或复核时间。</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="str">
+        <x:v>2026-06-23 12:00</x:v>
+      </x:c>
+      <x:c r="H19" s="11" t="str">
+        <x:v>系统生成</x:v>
+      </x:c>
+      <x:c r="I19" s="11" t="str">
+        <x:v>每次更新</x:v>
+      </x:c>
+      <x:c r="J19" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3159,10 +3239,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>course_id</x:v>
+        <x:v>competition_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>课程ID</x:v>
+        <x:v>赛事ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>string</x:v>
@@ -3174,13 +3254,13 @@
         <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>课程主键。</x:v>
+        <x:v>赛事主键。</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>course_bim_app</x:v>
+        <x:v>comp_vscc_bim_2026</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>系统生成/课程导入</x:v>
+        <x:v>系统生成/赛事采集</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
         <x:v>创建时</x:v>
@@ -3189,103 +3269,101 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>course_code</x:v>
+        <x:v>competition_name</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>课程代码</x:v>
+        <x:v>赛事名称</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>UK</x:v>
+        <x:v>IDX</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>学校或专业课程代码。</x:v>
+        <x:v>赛事或赛项名称。</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>ZNJZ-BIM-002</x:v>
+        <x:v>建筑信息模型建模与应用</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>培养方案/教务系统</x:v>
+        <x:v>赛事官网</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>按学年</x:v>
+        <x:v>按赛事年度</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>course_name</x:v>
+        <x:v>competition_level</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>课程名称</x:v>
+        <x:v>赛事级别</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>课程名称。</x:v>
+        <x:v>国家级、国际级、省级、行业级、校级。</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>建筑信息模型应用</x:v>
+        <x:v>国家级</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>培养方案/课程库</x:v>
+        <x:v>赛事官网/政策文件</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>按学年</x:v>
+        <x:v>按赛事年度</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>major_id</x:v>
+        <x:v>organizer</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>专业ID</x:v>
+        <x:v>主办单位</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str">
-        <x:v>课程所属专业。</x:v>
+        <x:v>赛事主办或承办单位。</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>maj_460301</x:v>
+        <x:v>教育部等</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>专业库</x:v>
+        <x:v>赛事官网/通知</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>按学年</x:v>
+        <x:v>按赛事年度</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>course_type</x:v>
+        <x:v>event_category</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>课程类型</x:v>
+        <x:v>赛项类别</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
         <x:v>否</x:v>
@@ -3294,109 +3372,111 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>公共基础、专业基础、专业核心、实践课程。</x:v>
+        <x:v>技能竞赛、创新创业竞赛、行业赛项等。</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>专业核心</x:v>
+        <x:v>职业院校技能竞赛</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>培养方案</x:v>
+        <x:v>赛事官网</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>按学年</x:v>
+        <x:v>按赛事年度</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>credits</x:v>
+        <x:v>major_codes</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>学分</x:v>
+        <x:v>适配专业</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str">
-        <x:v>课程学分。</x:v>
+        <x:v>赛项可关联专业代码。</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>4</x:v>
+        <x:v>440301,440305</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>培养方案</x:v>
+        <x:v>赛项规程/人工维护</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>按学年</x:v>
+        <x:v>按赛事年度</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>hours</x:v>
+        <x:v>ability_requirements</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>学时</x:v>
+        <x:v>能力要求</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str">
-        <x:v>课程学时。</x:v>
+        <x:v>赛项考查能力。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>64</x:v>
+        <x:v>模型建立、协同应用、成果表达</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>培养方案</x:v>
+        <x:v>赛项规程</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>按学年</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="str"/>
-    </x:row>
-    <x:row r="9" ht="24" hidden="0" customHeight="1">
+        <x:v>按赛事年度</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str">
+        <x:v>关联08_岗位能力库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="12" t="str">
-        <x:v>job_ids</x:v>
+        <x:v>competition_rules_url</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>关联岗位</x:v>
+        <x:v>赛项规程链接</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>url</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str">
-        <x:v>课程支撑岗位ID列表。</x:v>
+        <x:v>赛项规程、通知或指南链接。</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>job_bim_deepening,job_project_digital_manager</x:v>
+        <x:v>https://www.chinaskills-jsw.org/</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>岗位-课程映射</x:v>
+        <x:v>赛事官网</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
-        <x:v>按项目维护</x:v>
+        <x:v>随采集</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
     </x:row>
-    <x:row r="10" ht="24" hidden="0" customHeight="1">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="12" t="str">
-        <x:v>ability_ids</x:v>
+        <x:v>award_info</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>关联能力项</x:v>
+        <x:v>获奖信息</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>text</x:v>
@@ -3406,25 +3486,25 @@
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str">
-        <x:v>课程支撑能力项ID列表。</x:v>
+        <x:v>获奖等级、团队、学校等。</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>ability_bim_model,ability_coordination</x:v>
+        <x:v>一等奖</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>能力映射</x:v>
+        <x:v>赛事官网/学校资料</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
-        <x:v>按项目维护</x:v>
+        <x:v>按赛事年度</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="12" t="str">
-        <x:v>practice_project</x:v>
+        <x:v>result_transform</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>实训项目</x:v>
+        <x:v>成果转化方向</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>text</x:v>
@@ -3434,18 +3514,46 @@
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str">
-        <x:v>课程承接的项目化实训。</x:v>
+        <x:v>赛项成果与课程、实训、证书的转化。</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>BIM模型综合深化实训</x:v>
+        <x:v>转化为BIM综合实训项目</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>课程资料/赛事转化</x:v>
+        <x:v>人工维护</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
-        <x:v>按学年</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="12" t="str">
+        <x:v>source_url</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>来源链接</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>url</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str"/>
+      <x:c r="F12" s="11" t="str">
+        <x:v>赛事来源URL。</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str">
+        <x:v>https://www.chinaskills-jsw.org/</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="str">
+        <x:v>数据来源库</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="str">
+        <x:v>随采集</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3502,10 +3610,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>policy_id</x:v>
+        <x:v>certificate_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>政策ID</x:v>
+        <x:v>证书ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>string</x:v>
@@ -3517,25 +3625,25 @@
         <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>政策记录主键。</x:v>
+        <x:v>证书主键。</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>policy_moe_2026_001</x:v>
+        <x:v>cert_bim_middle</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>系统生成/政策采集</x:v>
+        <x:v>系统生成/证书采集</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
-        <x:v>采集时</x:v>
+        <x:v>创建时</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str"/>
     </x:row>
-    <x:row r="3" ht="24" hidden="0" customHeight="1">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>policy_title</x:v>
+        <x:v>certificate_name</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>政策标题</x:v>
+        <x:v>证书名称</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>string</x:v>
@@ -3547,28 +3655,28 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>政策或新闻标题。</x:v>
+        <x:v>证书标准名称。</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>关于实施中国特色高水平高职学校和专业建设计划的通知</x:v>
+        <x:v>建筑信息模型职业技能等级证书</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>官网采集</x:v>
+        <x:v>证书平台/职业资格目录</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>高频/按发布</x:v>
+        <x:v>按官方更新</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>issuer</x:v>
+        <x:v>certificate_type</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>发布机构</x:v>
+        <x:v>证书类型</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>是</x:v>
@@ -3577,58 +3685,58 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>政策发布机构。</x:v>
+        <x:v>职业资格、职业技能等级、1+X、行业证书等。</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>教育部</x:v>
+        <x:v>职业技能等级证书</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>官网采集</x:v>
+        <x:v>证书平台</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>高频/按发布</x:v>
+        <x:v>按官方更新</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>publish_date</x:v>
+        <x:v>level</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>发布日期</x:v>
+        <x:v>证书等级</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>date</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>政策发布日期。</x:v>
+        <x:v>初级、中级、高级或专项。</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>中级</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>官网采集</x:v>
+        <x:v>证书平台</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>高频/按发布</x:v>
+        <x:v>按官方更新</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>policy_level</x:v>
+        <x:v>issuer</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>政策层级</x:v>
+        <x:v>颁发/评价机构</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
         <x:v>否</x:v>
@@ -3637,25 +3745,25 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>国家、省、市、行业、学校。</x:v>
+        <x:v>证书颁发或评价组织。</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>国家</x:v>
+        <x:v>评价组织名称</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>规则归类</x:v>
+        <x:v>证书平台/目录</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>采集时</x:v>
+        <x:v>按官方更新</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>region</x:v>
+        <x:v>occupation_code</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>适用区域</x:v>
+        <x:v>对应职业/工种编码</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>string</x:v>
@@ -3664,28 +3772,30 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>IDX</x:v>
+        <x:v>FK</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>全国或具体省市。</x:v>
+        <x:v>证书对应职业编码或工种编码。</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>全国</x:v>
+        <x:v>4-04-05-04</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>规则归类/政策正文</x:v>
+        <x:v>职业资格目录/职业标准</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>采集时</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="str"/>
+        <x:v>按官方更新</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str">
+        <x:v>关联05_职业库</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>topic_tags</x:v>
+        <x:v>exam_items</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>政策标签</x:v>
+        <x:v>考试科目/考核内容</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>text</x:v>
@@ -3693,29 +3803,27 @@
       <x:c r="D8" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+      <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str">
-        <x:v>职业教育、高等教育、就业创业、产教融合、技能人才等。</x:v>
+        <x:v>考试科目、技能考核模块。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>职业教育、产教融合</x:v>
+        <x:v>理论知识、实操考核</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>NLP抽取/人工复核</x:v>
+        <x:v>证书说明/评价规范</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>采集时</x:v>
+        <x:v>按官方更新</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="12" t="str">
-        <x:v>related_chain_ids</x:v>
+        <x:v>requirements</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>关联产业链</x:v>
+        <x:v>报考条件</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>text</x:v>
@@ -3725,53 +3833,53 @@
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str">
-        <x:v>政策关联产业链。</x:v>
+        <x:v>报考条件或适用人群。</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>chain_smart_manufacturing</x:v>
+        <x:v>相关专业在校生或从业人员</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>规则匹配/人工维护</x:v>
+        <x:v>证书说明/评价规范</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
-        <x:v>按批次</x:v>
+        <x:v>按官方更新</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="12" t="str">
-        <x:v>related_major_codes</x:v>
+        <x:v>valid_period</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>关联专业</x:v>
+        <x:v>有效期</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str">
-        <x:v>政策关联专业。</x:v>
+        <x:v>证书有效期。</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>460301,510205</x:v>
+        <x:v>长期有效/以官网为准</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>规则匹配/人工维护</x:v>
+        <x:v>证书说明</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
-        <x:v>按批次</x:v>
+        <x:v>按官方更新</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
     </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
+    <x:row r="11" ht="24" hidden="0" customHeight="1">
       <x:c r="A11" s="12" t="str">
-        <x:v>related_job_ids</x:v>
+        <x:v>fit_job_ids</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>关联岗位</x:v>
+        <x:v>适用岗位</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>text</x:v>
@@ -3781,25 +3889,25 @@
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str">
-        <x:v>政策关联岗位。</x:v>
+        <x:v>适配岗位ID列表。</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>job_bim_deepening</x:v>
+        <x:v>job_bim_modeler,job_bim_deepening</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>规则匹配/人工维护</x:v>
+        <x:v>岗位-证书映射</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
-        <x:v>按批次</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
     </x:row>
-    <x:row r="12" ht="24" hidden="0" customHeight="1">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="12" t="str">
-        <x:v>summary</x:v>
+        <x:v>fit_major_codes</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>政策摘要</x:v>
+        <x:v>适配专业</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>text</x:v>
@@ -3809,16 +3917,16 @@
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str">
-        <x:v>政策要点摘要。</x:v>
+        <x:v>适配专业代码列表。</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>支持高水平专业群建设和产教融合项目</x:v>
+        <x:v>440301,440305</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
-        <x:v>AI摘要后人工审核</x:v>
+        <x:v>证书说明/人工维护</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
-        <x:v>采集时</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str"/>
     </x:row>
@@ -3837,46 +3945,18 @@
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str">
-        <x:v>政策正文链接。</x:v>
+        <x:v>证书查询或目录来源URL。</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/</x:v>
+        <x:v>https://zscx.osta.org.cn/</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str">
-        <x:v>官网采集</x:v>
+        <x:v>数据来源库</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str">
-        <x:v>采集时</x:v>
+        <x:v>随采集</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str"/>
-    </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="12" t="str">
-        <x:v>crawl_time</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="str">
-        <x:v>采集时间</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="str">
-        <x:v>datetime</x:v>
-      </x:c>
-      <x:c r="D14" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="str"/>
-      <x:c r="F14" s="11" t="str">
-        <x:v>系统采集时间。</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="str">
-        <x:v>2026-06-22 10:00</x:v>
-      </x:c>
-      <x:c r="H14" s="11" t="str">
-        <x:v>采集任务</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="str">
-        <x:v>每次采集</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3933,10 +4013,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>batch_id</x:v>
+        <x:v>course_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>初始化批次ID</x:v>
+        <x:v>课程ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>string</x:v>
@@ -3948,58 +4028,58 @@
         <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>一次专业数据初始化任务主键。</x:v>
+        <x:v>课程主键。</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>init_20260622_001</x:v>
+        <x:v>course_bim_app</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>系统生成</x:v>
+        <x:v>系统生成/课程导入</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
-        <x:v>每次初始化</x:v>
+        <x:v>创建时</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>major_id</x:v>
+        <x:v>course_code</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>专业ID</x:v>
+        <x:v>课程代码</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>FK</x:v>
+        <x:v>UK</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>被初始化的专业。</x:v>
+        <x:v>学校或专业课程代码。</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>maj_460301</x:v>
+        <x:v>ZNJZ-BIM-002</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>专业库</x:v>
+        <x:v>培养方案/教务系统</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>每次初始化</x:v>
+        <x:v>按学年</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>status</x:v>
+        <x:v>course_name</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>状态</x:v>
+        <x:v>课程名称</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>是</x:v>
@@ -4008,199 +4088,197 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>idle、initializing、ready、failed。</x:v>
+        <x:v>课程名称。</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>ready</x:v>
+        <x:v>建筑信息模型应用</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>系统状态</x:v>
+        <x:v>培养方案/课程库</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>实时</x:v>
+        <x:v>按学年</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>input_summary</x:v>
+        <x:v>major_id</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>输入资料摘要</x:v>
+        <x:v>专业ID</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="str"/>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>FK</x:v>
+      </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>专业基础信息、人培资料、岗位资料等摘要。</x:v>
+        <x:v>课程所属专业。</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>已上传人培方案和岗位资料</x:v>
+        <x:v>maj_460301</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>CMS/上传资料</x:v>
+        <x:v>专业库</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>每次初始化</x:v>
+        <x:v>按学年</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str"/>
     </x:row>
-    <x:row r="6" ht="24" hidden="0" customHeight="1">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>source_summary</x:v>
+        <x:v>course_type</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>来源摘要</x:v>
+        <x:v>课程类型</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="str"/>
+      <x:c r="E6" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>本次初始化使用的来源集合。</x:v>
+        <x:v>公共基础、专业基础、专业核心、实践课程。</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>专业目录、产业链库、招聘批次202606</x:v>
+        <x:v>专业核心</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>数据来源库/采集批次</x:v>
+        <x:v>培养方案</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>每次初始化</x:v>
+        <x:v>按学年</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>selected_chain_id</x:v>
+        <x:v>credits</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>默认产业链ID</x:v>
+        <x:v>学分</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str">
-        <x:v>管理员选择的默认产业链。</x:v>
+        <x:v>课程学分。</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>chain_smart_construction</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>CMS操作</x:v>
+        <x:v>培养方案</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>按操作</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="str">
-        <x:v>关联03_产业链库</x:v>
-      </x:c>
+        <x:v>按学年</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>created_by</x:v>
+        <x:v>hours</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>创建人</x:v>
+        <x:v>学时</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str">
-        <x:v>发起初始化的用户。</x:v>
+        <x:v>课程学时。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>刘鸿喆</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>系统登录态</x:v>
+        <x:v>培养方案</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>每次初始化</x:v>
+        <x:v>按学年</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str"/>
     </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
+    <x:row r="9" ht="24" hidden="0" customHeight="1">
       <x:c r="A9" s="12" t="str">
-        <x:v>created_at</x:v>
+        <x:v>job_ids</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>创建时间</x:v>
+        <x:v>关联岗位</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>datetime</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str">
-        <x:v>任务创建时间。</x:v>
+        <x:v>课程支撑岗位ID列表。</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>2026-06-22 10:00</x:v>
+        <x:v>job_bim_deepening,job_project_digital_manager</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>系统生成</x:v>
+        <x:v>岗位-课程映射</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
-        <x:v>每次初始化</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str"/>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
+    <x:row r="10" ht="24" hidden="0" customHeight="1">
       <x:c r="A10" s="12" t="str">
-        <x:v>completed_at</x:v>
+        <x:v>ability_ids</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>完成时间</x:v>
+        <x:v>关联能力项</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>datetime</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str">
-        <x:v>任务完成时间。</x:v>
+        <x:v>课程支撑能力项ID列表。</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>2026-06-22 10:05</x:v>
+        <x:v>ability_bim_model,ability_coordination</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>系统生成</x:v>
+        <x:v>能力映射</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
-        <x:v>每次初始化</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="12" t="str">
-        <x:v>error_message</x:v>
+        <x:v>practice_project</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>失败原因</x:v>
+        <x:v>实训项目</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>text</x:v>
@@ -4210,16 +4288,16 @@
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str">
-        <x:v>失败时记录错误原因。</x:v>
+        <x:v>课程承接的项目化实训。</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>招聘源不可访问</x:v>
+        <x:v>BIM模型综合深化实训</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>系统生成</x:v>
+        <x:v>课程资料/赛事转化</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
-        <x:v>失败时</x:v>
+        <x:v>按学年</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str"/>
     </x:row>
@@ -4232,891 +4310,427 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="33.33000183105469" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="46.66999816894531" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="26.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28.889999389648438" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="10" t="str">
-        <x:v>模块</x:v>
+        <x:v>字段编码</x:v>
       </x:c>
       <x:c r="B1" s="10" t="str">
-        <x:v>来源名称</x:v>
+        <x:v>中文名称</x:v>
       </x:c>
       <x:c r="C1" s="10" t="str">
-        <x:v>网址</x:v>
+        <x:v>数据类型</x:v>
       </x:c>
       <x:c r="D1" s="10" t="str">
-        <x:v>用途</x:v>
+        <x:v>是否必填</x:v>
       </x:c>
       <x:c r="E1" s="10" t="str">
-        <x:v>来源类型</x:v>
+        <x:v>键/索引</x:v>
       </x:c>
       <x:c r="F1" s="10" t="str">
-        <x:v>建议更新频率</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="24" hidden="0" customHeight="1">
-      <x:c r="A2" s="11" t="str">
-        <x:v>专业数据库</x:v>
+        <x:v>字段说明/口径</x:v>
+      </x:c>
+      <x:c r="G1" s="10" t="str">
+        <x:v>示例值</x:v>
+      </x:c>
+      <x:c r="H1" s="10" t="str">
+        <x:v>来源/生成方式</x:v>
+      </x:c>
+      <x:c r="I1" s="10" t="str">
+        <x:v>更新频率</x:v>
+      </x:c>
+      <x:c r="J1" s="10" t="str">
+        <x:v>关联对象/备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="12" t="str">
+        <x:v>policy_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>教育部《职业教育专业目录（2021年）》</x:v>
+        <x:v>政策ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A07/moe_953/202103/t20210319_521135.html</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>专业代码、专业名称、层次、大类、专业类</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>官方文件</x:v>
+        <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>低频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="11" t="str">
-        <x:v>专业数据库</x:v>
+        <x:v>政策记录主键。</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str">
+        <x:v>policy_moe_2026_001</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="str">
+        <x:v>系统生成/政策采集</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="str">
+        <x:v>采集时</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="str"/>
+    </x:row>
+    <x:row r="3" ht="24" hidden="0" customHeight="1">
+      <x:c r="A3" s="12" t="str">
+        <x:v>policy_title</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>教育部职业教育专业简介</x:v>
+        <x:v>政策标题</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>https://www.moe.gov.cn/jyb_zzjg/moe_674/2022/2022_zjzyml/</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>培养目标、就业面向、核心课程、职业面向</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>官方栏目</x:v>
+        <x:v>IDX</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>低频</x:v>
-      </x:c>
+        <x:v>政策或新闻标题。</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="str">
+        <x:v>关于实施中国特色高水平高职学校和专业建设计划的通知</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="str">
+        <x:v>官网采集</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="str">
+        <x:v>高频/按发布</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="str"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="11" t="str">
-        <x:v>专业数据库</x:v>
+      <x:c r="A4" s="12" t="str">
+        <x:v>issuer</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>阳光高考专业库</x:v>
+        <x:v>发布机构</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>https://gaokao.chsi.com.cn/zyk/zybk/</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>普通本科专业信息补充</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>官方平台</x:v>
+        <x:v>IDX</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>低频</x:v>
-      </x:c>
+        <x:v>政策发布机构。</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="str">
+        <x:v>教育部</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="str">
+        <x:v>官网采集</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="str">
+        <x:v>高频/按发布</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="11" t="str">
-        <x:v>专业数据库</x:v>
+      <x:c r="A5" s="12" t="str">
+        <x:v>publish_date</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>教育部政策文件检索</x:v>
+        <x:v>发布日期</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
+        <x:v>date</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>政策发布日期。</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>2026-06-01</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str">
+        <x:v>官网采集</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="str">
+        <x:v>高频/按发布</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="str"/>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="12" t="str">
+        <x:v>policy_level</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>政策层级</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>国家、省、市、行业、学校。</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>国家</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="str">
+        <x:v>规则归类</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="str">
+        <x:v>采集时</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str"/>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="12" t="str">
+        <x:v>region</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>适用区域</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>全国或具体省市。</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="str">
+        <x:v>全国</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="str">
+        <x:v>规则归类/政策正文</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="str">
+        <x:v>采集时</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str"/>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="12" t="str">
+        <x:v>topic_tags</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>政策标签</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>职业教育、高等教育、就业创业、产教融合、技能人才等。</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>职业教育、产教融合</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str">
+        <x:v>NLP抽取/人工复核</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="str">
+        <x:v>采集时</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str"/>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="12" t="str">
+        <x:v>related_chain_ids</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>关联产业链</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str"/>
+      <x:c r="F9" s="11" t="str">
+        <x:v>政策关联产业链。</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="str">
+        <x:v>chain_smart_manufacturing</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="str">
+        <x:v>规则匹配/人工维护</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str"/>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="12" t="str">
+        <x:v>related_major_codes</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>关联专业</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str"/>
+      <x:c r="F10" s="11" t="str">
+        <x:v>政策关联专业。</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>460301,510205</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="str">
+        <x:v>规则匹配/人工维护</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="str">
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="str"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="12" t="str">
+        <x:v>related_job_ids</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>关联岗位</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str"/>
+      <x:c r="F11" s="11" t="str">
+        <x:v>政策关联岗位。</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str">
+        <x:v>job_bim_deepening</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str">
+        <x:v>规则匹配/人工维护</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="str">
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="str"/>
+    </x:row>
+    <x:row r="12" ht="24" hidden="0" customHeight="1">
+      <x:c r="A12" s="12" t="str">
+        <x:v>summary</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>政策摘要</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str"/>
+      <x:c r="F12" s="11" t="str">
+        <x:v>政策要点摘要。</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str">
+        <x:v>支持高水平专业群建设和产教融合项目</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="str">
+        <x:v>AI摘要后人工审核</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="str">
+        <x:v>采集时</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="str"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="12" t="str">
+        <x:v>source_url</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>来源链接</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>url</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str"/>
+      <x:c r="F13" s="11" t="str">
+        <x:v>政策正文链接。</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str">
         <x:v>https://www.moe.gov.cn/srcsite/</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>专业目录调整、专业设置备案审批通知</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="11" t="str">
-        <x:v>行业数据库</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="str">
-        <x:v>国家统计局《国民经济行业分类》</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>https://www.stats.gov.cn/sj/tjbz/gmjjhyfl/</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>行业代码、行业名称、行业层级</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="str">
-        <x:v>官方标准</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="str">
-        <x:v>低频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="11" t="str">
-        <x:v>行业数据库</x:v>
-      </x:c>
-      <x:c r="B7" s="11" t="str">
-        <x:v>国家统计局统计标准栏目</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="str">
-        <x:v>https://www.stats.gov.cn/sj/tjbz/</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="str">
-        <x:v>统计分类标准总入口</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="str">
-        <x:v>低频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="11" t="str">
-        <x:v>行业数据库</x:v>
-      </x:c>
-      <x:c r="B8" s="11" t="str">
-        <x:v>国家统计局统计用产品分类目录</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="str">
-        <x:v>https://www.stats.gov.cn/sj/tjbz/tjcpflml/</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="str">
-        <x:v>产品/服务分类补充</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="str">
-        <x:v>低频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="11" t="str">
-        <x:v>行业数据库</x:v>
-      </x:c>
-      <x:c r="B9" s="11" t="str">
-        <x:v>国家标准全文公开系统</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>https://openstd.samr.gov.cn/</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>GB/T标准核验</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="str">
-        <x:v>低频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="11" t="str">
-        <x:v>产业数据库</x:v>
-      </x:c>
-      <x:c r="B10" s="11" t="str">
-        <x:v>国家发改委政策发布栏目</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="str">
-        <x:v>https://www.ndrc.gov.cn/xxgk/zcfb/</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="str">
-        <x:v>产业政策、目录、规划</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="24" hidden="0" customHeight="1">
-      <x:c r="A11" s="11" t="str">
-        <x:v>产业数据库</x:v>
-      </x:c>
-      <x:c r="B11" s="11" t="str">
-        <x:v>《产业结构调整指导目录（2024年本）》</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="str">
-        <x:v>https://www.ndrc.gov.cn/xxgk/zcfb/fzggwl/202312/t20231229_1363133.html</x:v>
-      </x:c>
-      <x:c r="D11" s="11" t="str">
-        <x:v>产业鼓励/限制/淘汰口径</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="str">
-        <x:v>官方文件</x:v>
-      </x:c>
-      <x:c r="F11" s="11" t="str">
-        <x:v>低频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="11" t="str">
-        <x:v>产业数据库</x:v>
-      </x:c>
-      <x:c r="B12" s="11" t="str">
-        <x:v>工业和信息化部政策文件</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="str">
-        <x:v>https://www.miit.gov.cn/zwgk/zcwj/</x:v>
-      </x:c>
-      <x:c r="D12" s="11" t="str">
-        <x:v>工业、制造业、信息化政策</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="11" t="str">
-        <x:v>产业环节关系库</x:v>
-      </x:c>
-      <x:c r="B13" s="11" t="str">
-        <x:v>产业链图谱/桑基图人工复核记录</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="str"/>
-      <x:c r="D13" s="11" t="str">
-        <x:v>产业环节之间的上下游、支撑、协同关系和连线权重</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="str">
-        <x:v>运营维护记录</x:v>
-      </x:c>
-      <x:c r="F13" s="11" t="str">
-        <x:v>按版本</x:v>
-      </x:c>
+      <x:c r="H13" s="11" t="str">
+        <x:v>官网采集</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str">
+        <x:v>采集时</x:v>
+      </x:c>
+      <x:c r="J13" s="11" t="str"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="11" t="str">
-        <x:v>企业数据库</x:v>
+      <x:c r="A14" s="12" t="str">
+        <x:v>crawl_time</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>国家企业信用信息公示系统</x:v>
+        <x:v>采集时间</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>https://www.gsxt.gov.cn/</x:v>
+        <x:v>datetime</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>工商登记、统一社会信用代码、经营范围</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="11" t="str">
-        <x:v>企业数据库</x:v>
-      </x:c>
-      <x:c r="B15" s="11" t="str">
-        <x:v>信用中国</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="str">
-        <x:v>https://www.creditchina.gov.cn/</x:v>
-      </x:c>
-      <x:c r="D15" s="11" t="str">
-        <x:v>企业信用信息补充</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="11" t="str">
-        <x:v>企业数据库</x:v>
-      </x:c>
-      <x:c r="B16" s="11" t="str">
-        <x:v>上海证券交易所上市公司公告</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="str">
-        <x:v>https://www.sse.com.cn/disclosure/listedinfo/announcement/</x:v>
-      </x:c>
-      <x:c r="D16" s="11" t="str">
-        <x:v>上市公司公告</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F16" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="11" t="str">
-        <x:v>企业数据库</x:v>
-      </x:c>
-      <x:c r="B17" s="11" t="str">
-        <x:v>深圳证券交易所上市公司公告</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="str">
-        <x:v>https://www.szse.cn/disclosure/listed/notice/index.html</x:v>
-      </x:c>
-      <x:c r="D17" s="11" t="str">
-        <x:v>上市公司公告</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="11" t="str">
-        <x:v>企业数据库</x:v>
-      </x:c>
-      <x:c r="B18" s="11" t="str">
-        <x:v>北京证券交易所信息披露</x:v>
-      </x:c>
-      <x:c r="C18" s="11" t="str">
-        <x:v>https://www.bse.cn/disclosure/company.html</x:v>
-      </x:c>
-      <x:c r="D18" s="11" t="str">
-        <x:v>上市公司公告</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F18" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="24" hidden="0" customHeight="1">
-      <x:c r="A19" s="11" t="str">
-        <x:v>企业数据库</x:v>
-      </x:c>
-      <x:c r="B19" s="11" t="str">
-        <x:v>巨潮资讯网</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="str">
-        <x:v>https://www.cninfo.com.cn/</x:v>
-      </x:c>
-      <x:c r="D19" s="11" t="str">
-        <x:v>上市公司公告聚合</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="str">
-        <x:v>官方指定信息披露平台</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="11" t="str">
-        <x:v>职业数据库</x:v>
-      </x:c>
-      <x:c r="B20" s="11" t="str">
-        <x:v>人社部《中华人民共和国职业分类大典》专题</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="str">
-        <x:v>https://www.mohrss.gov.cn/SYrlzyhshbzb/ztzl/zyflzd/zyfldg/</x:v>
-      </x:c>
-      <x:c r="D20" s="11" t="str">
-        <x:v>职业分类、职业编码、职业名称</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="str">
-        <x:v>官方专题</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="str">
-        <x:v>低频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="11" t="str">
-        <x:v>职业数据库</x:v>
-      </x:c>
-      <x:c r="B21" s="11" t="str">
-        <x:v>人社部新职业信息发布</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="str">
-        <x:v>https://www.mohrss.gov.cn/SYrlzyhshbzb/ztzl/zyflzd/xzyxx/</x:v>
-      </x:c>
-      <x:c r="D21" s="11" t="str">
-        <x:v>新职业名称、发布日期、职业说明</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="str">
-        <x:v>官方专题</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="11" t="str">
-        <x:v>职业数据库</x:v>
-      </x:c>
-      <x:c r="B22" s="11" t="str">
-        <x:v>技能人才评价工作网职业分类系统</x:v>
-      </x:c>
-      <x:c r="C22" s="11" t="str">
-        <x:v>https://www.osta.org.cn/career</x:v>
-      </x:c>
-      <x:c r="D22" s="11" t="str">
-        <x:v>职业分类查询</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="str">
-        <x:v>低频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="11" t="str">
-        <x:v>职业数据库</x:v>
-      </x:c>
-      <x:c r="B23" s="11" t="str">
-        <x:v>技能人才评价工作网职业标准系统</x:v>
-      </x:c>
-      <x:c r="C23" s="11" t="str">
-        <x:v>https://www.osta.org.cn/skillStandard</x:v>
-      </x:c>
-      <x:c r="D23" s="11" t="str">
-        <x:v>职业标准、技能要求</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="11" t="str">
-        <x:v>职业数据库</x:v>
-      </x:c>
-      <x:c r="B24" s="11" t="str">
-        <x:v>技能人才评价工作网国家职业资格目录清单系统</x:v>
-      </x:c>
-      <x:c r="C24" s="11" t="str">
-        <x:v>https://www.osta.org.cn/evaluation</x:v>
-      </x:c>
-      <x:c r="D24" s="11" t="str">
-        <x:v>职业资格目录</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F24" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="11" t="str">
-        <x:v>赛事数据库</x:v>
-      </x:c>
-      <x:c r="B25" s="11" t="str">
-        <x:v>全国职业院校技能大赛官网</x:v>
-      </x:c>
-      <x:c r="C25" s="11" t="str">
-        <x:v>https://www.chinaskills-jsw.org/</x:v>
-      </x:c>
-      <x:c r="D25" s="11" t="str">
-        <x:v>赛项、规程、参赛专业、获奖信息</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="str">
-        <x:v>官方/赛事平台</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="str">
-        <x:v>按赛事年度</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="11" t="str">
-        <x:v>赛事数据库</x:v>
-      </x:c>
-      <x:c r="B26" s="11" t="str">
-        <x:v>世界技能组织 WorldSkills</x:v>
-      </x:c>
-      <x:c r="C26" s="11" t="str">
-        <x:v>https://worldskills.org/</x:v>
-      </x:c>
-      <x:c r="D26" s="11" t="str">
-        <x:v>国际技能赛项与职业标准参考</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="str">
-        <x:v>国际组织</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="str">
-        <x:v>按赛事年度</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="11" t="str">
-        <x:v>赛事数据库</x:v>
-      </x:c>
-      <x:c r="B27" s="11" t="str">
-        <x:v>中国国际大学生创新大赛/全国大学生创业服务网</x:v>
-      </x:c>
-      <x:c r="C27" s="11" t="str">
-        <x:v>https://cy.ncss.cn/</x:v>
-      </x:c>
-      <x:c r="D27" s="11" t="str">
-        <x:v>创新创业赛道、获奖名单、竞赛规则</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F27" s="11" t="str">
-        <x:v>按赛事年度</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="11" t="str">
-        <x:v>证书数据库</x:v>
-      </x:c>
-      <x:c r="B28" s="11" t="str">
-        <x:v>技能人才评价工作网</x:v>
-      </x:c>
-      <x:c r="C28" s="11" t="str">
-        <x:v>https://www.osta.org.cn/</x:v>
-      </x:c>
-      <x:c r="D28" s="11" t="str">
-        <x:v>证书查询和评价系统入口</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="15" hidden="0" customHeight="1">
-      <x:c r="A29" s="11" t="str">
-        <x:v>证书数据库</x:v>
-      </x:c>
-      <x:c r="B29" s="11" t="str">
-        <x:v>技能人员职业资格证书全国联网查询系统</x:v>
-      </x:c>
-      <x:c r="C29" s="11" t="str">
-        <x:v>https://zscx.osta.org.cn/</x:v>
-      </x:c>
-      <x:c r="D29" s="11" t="str">
-        <x:v>职业资格证书查询</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F29" s="11" t="str">
-        <x:v>实时/查询</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="11" t="str">
-        <x:v>证书数据库</x:v>
-      </x:c>
-      <x:c r="B30" s="11" t="str">
-        <x:v>职业技能等级证书全国联网查询系统</x:v>
-      </x:c>
-      <x:c r="C30" s="11" t="str">
-        <x:v>https://zscx.osta.org.cn/</x:v>
-      </x:c>
-      <x:c r="D30" s="11" t="str">
-        <x:v>职业技能等级证书查询</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="str">
-        <x:v>实时/查询</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="11" t="str">
-        <x:v>证书数据库</x:v>
-      </x:c>
-      <x:c r="B31" s="11" t="str">
-        <x:v>1+X职业技能等级证书信息管理服务平台</x:v>
-      </x:c>
-      <x:c r="C31" s="11" t="str">
-        <x:v>https://vslc.ncb.edu.cn/</x:v>
-      </x:c>
-      <x:c r="D31" s="11" t="str">
-        <x:v>1+X证书目录和信息管理</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="str">
-        <x:v>官方/项目平台</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="15" hidden="0" customHeight="1">
-      <x:c r="A32" s="11" t="str">
-        <x:v>岗位库/招聘信息库</x:v>
-      </x:c>
-      <x:c r="B32" s="11" t="str">
-        <x:v>中国公共招聘网</x:v>
-      </x:c>
-      <x:c r="C32" s="11" t="str">
-        <x:v>https://job.mohrss.gov.cn/</x:v>
-      </x:c>
-      <x:c r="D32" s="11" t="str">
-        <x:v>公共招聘岗位</x:v>
-      </x:c>
-      <x:c r="E32" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F32" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="11" t="str">
-        <x:v>岗位库/招聘信息库</x:v>
-      </x:c>
-      <x:c r="B33" s="11" t="str">
-        <x:v>国家大学生就业服务平台</x:v>
-      </x:c>
-      <x:c r="C33" s="11" t="str">
-        <x:v>https://www.ncss.cn/</x:v>
-      </x:c>
-      <x:c r="D33" s="11" t="str">
-        <x:v>高校毕业生岗位与招聘活动</x:v>
-      </x:c>
-      <x:c r="E33" s="11" t="str">
-        <x:v>官方平台</x:v>
-      </x:c>
-      <x:c r="F33" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="15" hidden="0" customHeight="1">
-      <x:c r="A34" s="11" t="str">
-        <x:v>招聘信息库</x:v>
-      </x:c>
-      <x:c r="B34" s="11" t="str">
-        <x:v>国聘</x:v>
-      </x:c>
-      <x:c r="C34" s="11" t="str">
-        <x:v>https://www.iguopin.com/</x:v>
-      </x:c>
-      <x:c r="D34" s="11" t="str">
-        <x:v>央国企及社会招聘岗位补充</x:v>
-      </x:c>
-      <x:c r="E34" s="11" t="str">
-        <x:v>招聘平台</x:v>
-      </x:c>
-      <x:c r="F34" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="15" hidden="0" customHeight="1">
-      <x:c r="A35" s="11" t="str">
-        <x:v>招聘信息库</x:v>
-      </x:c>
-      <x:c r="B35" s="11" t="str">
-        <x:v>智联招聘</x:v>
-      </x:c>
-      <x:c r="C35" s="11" t="str">
-        <x:v>https://www.zhaopin.com/</x:v>
-      </x:c>
-      <x:c r="D35" s="11" t="str">
-        <x:v>社会招聘岗位补充</x:v>
-      </x:c>
-      <x:c r="E35" s="11" t="str">
-        <x:v>招聘平台</x:v>
-      </x:c>
-      <x:c r="F35" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="15" hidden="0" customHeight="1">
-      <x:c r="A36" s="11" t="str">
-        <x:v>招聘信息库</x:v>
-      </x:c>
-      <x:c r="B36" s="11" t="str">
-        <x:v>前程无忧</x:v>
-      </x:c>
-      <x:c r="C36" s="11" t="str">
-        <x:v>https://www.51job.com/</x:v>
-      </x:c>
-      <x:c r="D36" s="11" t="str">
-        <x:v>社会招聘岗位补充</x:v>
-      </x:c>
-      <x:c r="E36" s="11" t="str">
-        <x:v>招聘平台</x:v>
-      </x:c>
-      <x:c r="F36" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="15" hidden="0" customHeight="1">
-      <x:c r="A37" s="11" t="str">
-        <x:v>招聘信息库</x:v>
-      </x:c>
-      <x:c r="B37" s="11" t="str">
-        <x:v>BOSS直聘</x:v>
-      </x:c>
-      <x:c r="C37" s="11" t="str">
-        <x:v>https://www.zhipin.com/</x:v>
-      </x:c>
-      <x:c r="D37" s="11" t="str">
-        <x:v>社会招聘岗位补充</x:v>
-      </x:c>
-      <x:c r="E37" s="11" t="str">
-        <x:v>招聘平台</x:v>
-      </x:c>
-      <x:c r="F37" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="15" hidden="0" customHeight="1">
-      <x:c r="A38" s="11" t="str">
-        <x:v>招聘信息库</x:v>
-      </x:c>
-      <x:c r="B38" s="11" t="str">
-        <x:v>猎聘</x:v>
-      </x:c>
-      <x:c r="C38" s="11" t="str">
-        <x:v>https://www.liepin.com/</x:v>
-      </x:c>
-      <x:c r="D38" s="11" t="str">
-        <x:v>中高端岗位补充</x:v>
-      </x:c>
-      <x:c r="E38" s="11" t="str">
-        <x:v>招聘平台</x:v>
-      </x:c>
-      <x:c r="F38" s="11" t="str">
-        <x:v>高频</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="15" hidden="0" customHeight="1">
-      <x:c r="A39" s="11" t="str">
-        <x:v>政策库</x:v>
-      </x:c>
-      <x:c r="B39" s="11" t="str">
-        <x:v>教育部工作动态</x:v>
-      </x:c>
-      <x:c r="C39" s="11" t="str">
-        <x:v>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/</x:v>
-      </x:c>
-      <x:c r="D39" s="11" t="str">
-        <x:v>教育政策新闻和工作动态</x:v>
-      </x:c>
-      <x:c r="E39" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F39" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="15" hidden="0" customHeight="1">
-      <x:c r="A40" s="11" t="str">
-        <x:v>政策库</x:v>
-      </x:c>
-      <x:c r="B40" s="11" t="str">
-        <x:v>教育部政策文件</x:v>
-      </x:c>
-      <x:c r="C40" s="11" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/</x:v>
-      </x:c>
-      <x:c r="D40" s="11" t="str">
-        <x:v>教育政策正文</x:v>
-      </x:c>
-      <x:c r="E40" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F40" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="15" hidden="0" customHeight="1">
-      <x:c r="A41" s="11" t="str">
-        <x:v>政策库</x:v>
-      </x:c>
-      <x:c r="B41" s="11" t="str">
-        <x:v>教育部职业教育与成人教育司</x:v>
-      </x:c>
-      <x:c r="C41" s="11" t="str">
-        <x:v>https://www.moe.gov.cn/s78/A07/</x:v>
-      </x:c>
-      <x:c r="D41" s="11" t="str">
-        <x:v>职业教育政策、通知、动态</x:v>
-      </x:c>
-      <x:c r="E41" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F41" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="15" hidden="0" customHeight="1">
-      <x:c r="A42" s="11" t="str">
-        <x:v>政策库</x:v>
-      </x:c>
-      <x:c r="B42" s="11" t="str">
-        <x:v>人社部信息公开</x:v>
-      </x:c>
-      <x:c r="C42" s="11" t="str">
-        <x:v>https://www.mohrss.gov.cn/xxgk2020/</x:v>
-      </x:c>
-      <x:c r="D42" s="11" t="str">
-        <x:v>就业、技能人才、职业资格政策</x:v>
-      </x:c>
-      <x:c r="E42" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F42" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="15" hidden="0" customHeight="1">
-      <x:c r="A43" s="11" t="str">
-        <x:v>政策库</x:v>
-      </x:c>
-      <x:c r="B43" s="11" t="str">
-        <x:v>国家发改委政策发布</x:v>
-      </x:c>
-      <x:c r="C43" s="11" t="str">
-        <x:v>https://www.ndrc.gov.cn/xxgk/zcfb/</x:v>
-      </x:c>
-      <x:c r="D43" s="11" t="str">
-        <x:v>产业、区域、发展改革政策</x:v>
-      </x:c>
-      <x:c r="E43" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F43" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="15" hidden="0" customHeight="1">
-      <x:c r="A44" s="11" t="str">
-        <x:v>政策库</x:v>
-      </x:c>
-      <x:c r="B44" s="11" t="str">
-        <x:v>工业和信息化部政策文件</x:v>
-      </x:c>
-      <x:c r="C44" s="11" t="str">
-        <x:v>https://www.miit.gov.cn/zwgk/zcwj/</x:v>
-      </x:c>
-      <x:c r="D44" s="11" t="str">
-        <x:v>工业和信息化政策</x:v>
-      </x:c>
-      <x:c r="E44" s="11" t="str">
-        <x:v>官方栏目</x:v>
-      </x:c>
-      <x:c r="F44" s="11" t="str">
-        <x:v>按发布</x:v>
-      </x:c>
+        <x:v>系统采集时间。</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="str">
+        <x:v>2026-06-22 10:00</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="str">
+        <x:v>采集任务</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="str">
+        <x:v>每次采集</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5572,6 +5186,1282 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="16.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="26.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28.889999389648438" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="10" t="str">
+        <x:v>字段编码</x:v>
+      </x:c>
+      <x:c r="B1" s="10" t="str">
+        <x:v>中文名称</x:v>
+      </x:c>
+      <x:c r="C1" s="10" t="str">
+        <x:v>数据类型</x:v>
+      </x:c>
+      <x:c r="D1" s="10" t="str">
+        <x:v>是否必填</x:v>
+      </x:c>
+      <x:c r="E1" s="10" t="str">
+        <x:v>键/索引</x:v>
+      </x:c>
+      <x:c r="F1" s="10" t="str">
+        <x:v>字段说明/口径</x:v>
+      </x:c>
+      <x:c r="G1" s="10" t="str">
+        <x:v>示例值</x:v>
+      </x:c>
+      <x:c r="H1" s="10" t="str">
+        <x:v>来源/生成方式</x:v>
+      </x:c>
+      <x:c r="I1" s="10" t="str">
+        <x:v>更新频率</x:v>
+      </x:c>
+      <x:c r="J1" s="10" t="str">
+        <x:v>关联对象/备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="12" t="str">
+        <x:v>batch_id</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>初始化批次ID</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>一次专业数据初始化任务主键。</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str">
+        <x:v>init_20260622_001</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="str">
+        <x:v>系统生成</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="str">
+        <x:v>每次初始化</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="str"/>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="12" t="str">
+        <x:v>major_id</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>专业ID</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>被初始化的专业。</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="str">
+        <x:v>maj_460301</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="str">
+        <x:v>专业库</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="str">
+        <x:v>每次初始化</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="str"/>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="12" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>idle、initializing、ready、failed。</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="str">
+        <x:v>系统状态</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="str">
+        <x:v>实时</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str"/>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="12" t="str">
+        <x:v>input_summary</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>输入资料摘要</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str"/>
+      <x:c r="F5" s="11" t="str">
+        <x:v>专业基础信息、人培资料、岗位资料等摘要。</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>已上传人培方案和岗位资料</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str">
+        <x:v>CMS/上传资料</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="str">
+        <x:v>每次初始化</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="str"/>
+    </x:row>
+    <x:row r="6" ht="24" hidden="0" customHeight="1">
+      <x:c r="A6" s="12" t="str">
+        <x:v>source_summary</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>来源摘要</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str"/>
+      <x:c r="F6" s="11" t="str">
+        <x:v>本次初始化使用的来源集合。</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>专业目录、产业链库、招聘批次202606</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="str">
+        <x:v>数据来源库/采集批次</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="str">
+        <x:v>每次初始化</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str"/>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="12" t="str">
+        <x:v>selected_chain_id</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>默认产业链ID</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>管理员选择的默认产业链。</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="str">
+        <x:v>chain_smart_construction</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="str">
+        <x:v>CMS操作</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="str">
+        <x:v>按操作</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str">
+        <x:v>关联03_产业链库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="12" t="str">
+        <x:v>created_by</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>创建人</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str"/>
+      <x:c r="F8" s="11" t="str">
+        <x:v>发起初始化的用户。</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>刘鸿喆</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str">
+        <x:v>系统登录态</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="str">
+        <x:v>每次初始化</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str"/>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="12" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>datetime</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>任务创建时间。</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="str">
+        <x:v>2026-06-22 10:00</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="str">
+        <x:v>系统生成</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
+        <x:v>每次初始化</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str"/>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="12" t="str">
+        <x:v>completed_at</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>完成时间</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>datetime</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str"/>
+      <x:c r="F10" s="11" t="str">
+        <x:v>任务完成时间。</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>2026-06-22 10:05</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="str">
+        <x:v>系统生成</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="str">
+        <x:v>每次初始化</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="str"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="12" t="str">
+        <x:v>error_message</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>失败原因</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str"/>
+      <x:c r="F11" s="11" t="str">
+        <x:v>失败时记录错误原因。</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str">
+        <x:v>招聘源不可访问</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str">
+        <x:v>系统生成</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="str">
+        <x:v>失败时</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="33.33000183105469" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="46.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15.5600004196167" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="10" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="B1" s="10" t="str">
+        <x:v>来源名称</x:v>
+      </x:c>
+      <x:c r="C1" s="10" t="str">
+        <x:v>网址</x:v>
+      </x:c>
+      <x:c r="D1" s="10" t="str">
+        <x:v>用途</x:v>
+      </x:c>
+      <x:c r="E1" s="10" t="str">
+        <x:v>来源类型</x:v>
+      </x:c>
+      <x:c r="F1" s="10" t="str">
+        <x:v>建议更新频率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" hidden="0" customHeight="1">
+      <x:c r="A2" s="11" t="str">
+        <x:v>专业数据库</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>教育部《职业教育专业目录（2021年）》</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A07/moe_953/202103/t20210319_521135.html</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>专业代码、专业名称、层次、大类、专业类</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>官方文件</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>低频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="11" t="str">
+        <x:v>专业数据库</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>教育部职业教育专业简介</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>https://www.moe.gov.cn/jyb_zzjg/moe_674/2022/2022_zjzyml/</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>培养目标、就业面向、核心课程、职业面向</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>低频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="11" t="str">
+        <x:v>专业数据库</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>阳光高考专业库</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>https://gaokao.chsi.com.cn/zyk/zybk/</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>普通本科专业信息补充</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>低频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="11" t="str">
+        <x:v>专业数据库</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>教育部政策文件检索</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>专业目录调整、专业设置备案审批通知</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="11" t="str">
+        <x:v>行业数据库</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>国家统计局《国民经济行业分类》</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>https://www.stats.gov.cn/sj/tjbz/gmjjhyfl/</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>行业代码、行业名称、行业层级</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>官方标准</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>低频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="11" t="str">
+        <x:v>行业数据库</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>国家统计局统计标准栏目</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>https://www.stats.gov.cn/sj/tjbz/</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>统计分类标准总入口</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>低频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="11" t="str">
+        <x:v>行业数据库</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>国家统计局统计用产品分类目录</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>https://www.stats.gov.cn/sj/tjbz/tjcpflml/</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>产品/服务分类补充</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>低频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="11" t="str">
+        <x:v>行业数据库</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>国家标准全文公开系统</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>https://openstd.samr.gov.cn/</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>GB/T标准核验</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>低频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="11" t="str">
+        <x:v>产业数据库</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>国家发改委政策发布栏目</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>https://www.ndrc.gov.cn/xxgk/zcfb/</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>产业政策、目录、规划</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" hidden="0" customHeight="1">
+      <x:c r="A11" s="11" t="str">
+        <x:v>产业数据库</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>《产业结构调整指导目录（2024年本）》</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>https://www.ndrc.gov.cn/xxgk/zcfb/fzggwl/202312/t20231229_1363133.html</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>产业鼓励/限制/淘汰口径</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>官方文件</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>低频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="11" t="str">
+        <x:v>产业数据库</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>工业和信息化部政策文件</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>https://www.miit.gov.cn/zwgk/zcwj/</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>工业、制造业、信息化政策</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="11" t="str">
+        <x:v>产业环节关系库</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>产业链图谱/桑基图人工复核记录</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str"/>
+      <x:c r="D13" s="11" t="str">
+        <x:v>产业环节之间的上下游、支撑、协同关系和连线权重</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>运营维护记录</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="str">
+        <x:v>按版本</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="11" t="str">
+        <x:v>企业数据库</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>国家企业信用信息公示系统</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>https://www.gsxt.gov.cn/</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>工商登记、统一社会信用代码、经营范围</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="str">
+        <x:v>按批次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="11" t="str">
+        <x:v>企业数据库</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="str">
+        <x:v>信用中国</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>https://www.creditchina.gov.cn/</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>企业信用信息补充</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="str">
+        <x:v>按批次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="11" t="str">
+        <x:v>企业数据库</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
+        <x:v>上海证券交易所上市公司公告</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>https://www.sse.com.cn/disclosure/listedinfo/announcement/</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="str">
+        <x:v>上市公司公告</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="11" t="str">
+        <x:v>企业数据库</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="str">
+        <x:v>深圳证券交易所上市公司公告</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>https://www.szse.cn/disclosure/listed/notice/index.html</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str">
+        <x:v>上市公司公告</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="11" t="str">
+        <x:v>企业数据库</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="str">
+        <x:v>北京证券交易所信息披露</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="str">
+        <x:v>https://www.bse.cn/disclosure/company.html</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="str">
+        <x:v>上市公司公告</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="24" hidden="0" customHeight="1">
+      <x:c r="A19" s="11" t="str">
+        <x:v>企业数据库</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="str">
+        <x:v>巨潮资讯网</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="str">
+        <x:v>https://www.cninfo.com.cn/</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="str">
+        <x:v>上市公司公告聚合</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="str">
+        <x:v>官方指定信息披露平台</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="11" t="str">
+        <x:v>职业数据库</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="str">
+        <x:v>人社部《中华人民共和国职业分类大典》专题</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="str">
+        <x:v>https://www.mohrss.gov.cn/SYrlzyhshbzb/ztzl/zyflzd/zyfldg/</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="str">
+        <x:v>职业分类、职业编码、职业名称</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="str">
+        <x:v>官方专题</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="str">
+        <x:v>低频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="11" t="str">
+        <x:v>职业数据库</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="str">
+        <x:v>人社部新职业信息发布</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="str">
+        <x:v>https://www.mohrss.gov.cn/SYrlzyhshbzb/ztzl/zyflzd/xzyxx/</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="str">
+        <x:v>新职业名称、发布日期、职业说明</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="str">
+        <x:v>官方专题</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="11" t="str">
+        <x:v>职业数据库</x:v>
+      </x:c>
+      <x:c r="B22" s="11" t="str">
+        <x:v>技能人才评价工作网职业分类系统</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="str">
+        <x:v>https://www.osta.org.cn/career</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="str">
+        <x:v>职业分类查询</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="str">
+        <x:v>低频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="11" t="str">
+        <x:v>职业数据库</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="str">
+        <x:v>技能人才评价工作网职业标准系统</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="str">
+        <x:v>https://www.osta.org.cn/skillStandard</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="str">
+        <x:v>职业标准、技能要求</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="11" t="str">
+        <x:v>职业数据库</x:v>
+      </x:c>
+      <x:c r="B24" s="11" t="str">
+        <x:v>技能人才评价工作网国家职业资格目录清单系统</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="str">
+        <x:v>https://www.osta.org.cn/evaluation</x:v>
+      </x:c>
+      <x:c r="D24" s="11" t="str">
+        <x:v>职业资格目录</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="11" t="str">
+        <x:v>赛事数据库</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="str">
+        <x:v>全国职业院校技能大赛官网</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="str">
+        <x:v>https://www.chinaskills-jsw.org/</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="str">
+        <x:v>赛项、规程、参赛专业、获奖信息</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="str">
+        <x:v>官方/赛事平台</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
+        <x:v>按赛事年度</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="11" t="str">
+        <x:v>赛事数据库</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="str">
+        <x:v>世界技能组织 WorldSkills</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="str">
+        <x:v>https://worldskills.org/</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="str">
+        <x:v>国际技能赛项与职业标准参考</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="str">
+        <x:v>国际组织</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="str">
+        <x:v>按赛事年度</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="11" t="str">
+        <x:v>赛事数据库</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="str">
+        <x:v>中国国际大学生创新大赛/全国大学生创业服务网</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str">
+        <x:v>https://cy.ncss.cn/</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="str">
+        <x:v>创新创业赛道、获奖名单、竞赛规则</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>按赛事年度</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="11" t="str">
+        <x:v>证书数据库</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="str">
+        <x:v>技能人才评价工作网</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="str">
+        <x:v>https://www.osta.org.cn/</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="str">
+        <x:v>证书查询和评价系统入口</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="11" t="str">
+        <x:v>证书数据库</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="str">
+        <x:v>技能人员职业资格证书全国联网查询系统</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="str">
+        <x:v>https://zscx.osta.org.cn/</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="str">
+        <x:v>职业资格证书查询</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="str">
+        <x:v>实时/查询</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="11" t="str">
+        <x:v>证书数据库</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="str">
+        <x:v>职业技能等级证书全国联网查询系统</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="str">
+        <x:v>https://zscx.osta.org.cn/</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="str">
+        <x:v>职业技能等级证书查询</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="str">
+        <x:v>实时/查询</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="11" t="str">
+        <x:v>证书数据库</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="str">
+        <x:v>1+X职业技能等级证书信息管理服务平台</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>https://vslc.ncb.edu.cn/</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>1+X证书目录和信息管理</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="str">
+        <x:v>官方/项目平台</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="11" t="str">
+        <x:v>岗位库/招聘信息库</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="str">
+        <x:v>中国公共招聘网</x:v>
+      </x:c>
+      <x:c r="C32" s="11" t="str">
+        <x:v>https://job.mohrss.gov.cn/</x:v>
+      </x:c>
+      <x:c r="D32" s="11" t="str">
+        <x:v>公共招聘岗位</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="str">
+        <x:v>高频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="11" t="str">
+        <x:v>岗位库/招聘信息库</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>国家大学生就业服务平台</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>https://www.ncss.cn/</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>高校毕业生岗位与招聘活动</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="str">
+        <x:v>官方平台</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>高频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="11" t="str">
+        <x:v>招聘信息库</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="str">
+        <x:v>国聘</x:v>
+      </x:c>
+      <x:c r="C34" s="11" t="str">
+        <x:v>https://www.iguopin.com/</x:v>
+      </x:c>
+      <x:c r="D34" s="11" t="str">
+        <x:v>央国企及社会招聘岗位补充</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="str">
+        <x:v>招聘平台</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="str">
+        <x:v>高频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="11" t="str">
+        <x:v>招聘信息库</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="str">
+        <x:v>智联招聘</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="str">
+        <x:v>https://www.zhaopin.com/</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>社会招聘岗位补充</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="str">
+        <x:v>招聘平台</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str">
+        <x:v>高频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="11" t="str">
+        <x:v>招聘信息库</x:v>
+      </x:c>
+      <x:c r="B36" s="11" t="str">
+        <x:v>前程无忧</x:v>
+      </x:c>
+      <x:c r="C36" s="11" t="str">
+        <x:v>https://www.51job.com/</x:v>
+      </x:c>
+      <x:c r="D36" s="11" t="str">
+        <x:v>社会招聘岗位补充</x:v>
+      </x:c>
+      <x:c r="E36" s="11" t="str">
+        <x:v>招聘平台</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="str">
+        <x:v>高频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="11" t="str">
+        <x:v>招聘信息库</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="str">
+        <x:v>BOSS直聘</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="str">
+        <x:v>https://www.zhipin.com/</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="str">
+        <x:v>社会招聘岗位补充</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="str">
+        <x:v>招聘平台</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="str">
+        <x:v>高频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" s="11" t="str">
+        <x:v>招聘信息库</x:v>
+      </x:c>
+      <x:c r="B38" s="11" t="str">
+        <x:v>猎聘</x:v>
+      </x:c>
+      <x:c r="C38" s="11" t="str">
+        <x:v>https://www.liepin.com/</x:v>
+      </x:c>
+      <x:c r="D38" s="11" t="str">
+        <x:v>中高端岗位补充</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="str">
+        <x:v>招聘平台</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="str">
+        <x:v>高频</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="11" t="str">
+        <x:v>政策库</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="str">
+        <x:v>教育部工作动态</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="str">
+        <x:v>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="str">
+        <x:v>教育政策新闻和工作动态</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
+      <x:c r="A40" s="11" t="str">
+        <x:v>政策库</x:v>
+      </x:c>
+      <x:c r="B40" s="11" t="str">
+        <x:v>教育部政策文件</x:v>
+      </x:c>
+      <x:c r="C40" s="11" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/</x:v>
+      </x:c>
+      <x:c r="D40" s="11" t="str">
+        <x:v>教育政策正文</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
+      <x:c r="A41" s="11" t="str">
+        <x:v>政策库</x:v>
+      </x:c>
+      <x:c r="B41" s="11" t="str">
+        <x:v>教育部职业教育与成人教育司</x:v>
+      </x:c>
+      <x:c r="C41" s="11" t="str">
+        <x:v>https://www.moe.gov.cn/s78/A07/</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
+        <x:v>职业教育政策、通知、动态</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="A42" s="11" t="str">
+        <x:v>政策库</x:v>
+      </x:c>
+      <x:c r="B42" s="11" t="str">
+        <x:v>人社部信息公开</x:v>
+      </x:c>
+      <x:c r="C42" s="11" t="str">
+        <x:v>https://www.mohrss.gov.cn/xxgk2020/</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="str">
+        <x:v>就业、技能人才、职业资格政策</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
+      <x:c r="A43" s="11" t="str">
+        <x:v>政策库</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="str">
+        <x:v>国家发改委政策发布</x:v>
+      </x:c>
+      <x:c r="C43" s="11" t="str">
+        <x:v>https://www.ndrc.gov.cn/xxgk/zcfb/</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="str">
+        <x:v>产业、区域、发展改革政策</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" s="11" t="str">
+        <x:v>政策库</x:v>
+      </x:c>
+      <x:c r="B44" s="11" t="str">
+        <x:v>工业和信息化部政策文件</x:v>
+      </x:c>
+      <x:c r="C44" s="11" t="str">
+        <x:v>https://www.miit.gov.cn/zwgk/zcwj/</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="str">
+        <x:v>工业和信息化政策</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="str">
+        <x:v>官方栏目</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="str">
+        <x:v>按发布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="24" hidden="0" customHeight="1">
+      <x:c r="A45" s="11" t="str">
+        <x:v>岗位资源匹配库</x:v>
+      </x:c>
+      <x:c r="B45" s="11" t="str">
+        <x:v>岗位画像资源匹配与专家复核记录</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="str"/>
+      <x:c r="D45" s="11" t="str">
+        <x:v>岗位画像中的推荐证书、对接专业、相关企业、课程实训和匹配依据</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="str">
+        <x:v>运营维护记录</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="str">
+        <x:v>按版本</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="24" hidden="0" customHeight="1">
+      <x:c r="A46" s="11" t="str">
+        <x:v>新技术岗位匹配库</x:v>
+      </x:c>
+      <x:c r="B46" s="11" t="str">
+        <x:v>新岗位新技术AI研判与专家复核记录</x:v>
+      </x:c>
+      <x:c r="C46" s="11" t="str"/>
+      <x:c r="D46" s="11" t="str">
+        <x:v>技术方向、成熟阶段、产业影响、新岗位、职业路径、专业/课程/能力建议</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="str">
+        <x:v>运营维护记录</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="str">
+        <x:v>按版本</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="17.780000686645508" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16.670000076293945" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="21.110000610351562" hidden="0" customWidth="1"/>
@@ -5902,141 +6792,401 @@
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="11" t="str">
-        <x:v>rel_company_industry</x:v>
+        <x:v>rel_resource_job</x:v>
       </x:c>
       <x:c r="B17" s="11" t="str">
-        <x:v>企业</x:v>
+        <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>行业</x:v>
+        <x:v>岗位</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
         <x:v>N:1</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str">
-        <x:v>industry_code</x:v>
+        <x:v>job_id -&gt; job_id</x:v>
       </x:c>
       <x:c r="F17" s="11" t="str">
-        <x:v>企业按国民经济行业分类归类。</x:v>
+        <x:v>岗位画像资源匹配归属具体岗位。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="11" t="str">
-        <x:v>rel_posting_job</x:v>
+        <x:v>rel_resource_major</x:v>
       </x:c>
       <x:c r="B18" s="11" t="str">
-        <x:v>招聘信息</x:v>
+        <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>岗位</x:v>
+        <x:v>专业</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>N:1</x:v>
+        <x:v>N:M</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>posting_id -&gt; job_id</x:v>
+        <x:v>major_codes -&gt; major_code</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
-        <x:v>原始招聘标题归一到岗位库。</x:v>
+        <x:v>岗位画像中的对接专业可回溯到专业库。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="11" t="str">
-        <x:v>rel_posting_company</x:v>
+        <x:v>rel_resource_certificate</x:v>
       </x:c>
       <x:c r="B19" s="11" t="str">
-        <x:v>招聘信息</x:v>
+        <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>企业</x:v>
+        <x:v>证书</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>N:1</x:v>
+        <x:v>N:M</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str">
-        <x:v>posting_id -&gt; company_id</x:v>
+        <x:v>certificate_ids -&gt; certificate_id</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>招聘企业归一到企业库。</x:v>
+        <x:v>岗位画像中的推荐证书可回溯到证书库。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="11" t="str">
-        <x:v>rel_trend_job</x:v>
+        <x:v>rel_resource_company</x:v>
       </x:c>
       <x:c r="B20" s="11" t="str">
-        <x:v>招聘趋势</x:v>
+        <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>岗位/产业链/城市</x:v>
+        <x:v>企业</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>聚合</x:v>
+        <x:v>N:M</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>period, chain_id, job_id, city</x:v>
+        <x:v>company_ids -&gt; company_id</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>按周期沉淀趋势统计，避免实时口径漂移。</x:v>
+        <x:v>岗位画像中的相关企业可回溯到企业库。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="11" t="str">
-        <x:v>rel_competition_major</x:v>
+        <x:v>rel_resource_ability</x:v>
       </x:c>
       <x:c r="B21" s="11" t="str">
-        <x:v>赛事</x:v>
+        <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>专业</x:v>
+        <x:v>岗位能力</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>competition_id, major_code</x:v>
+        <x:v>ability_ids -&gt; ability_id</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
-        <x:v>赛项适配专业。</x:v>
+        <x:v>专业、证书、企业推荐依据可追溯到岗位能力项。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="11" t="str">
-        <x:v>rel_competition_ability</x:v>
+        <x:v>rel_resource_course</x:v>
       </x:c>
       <x:c r="B22" s="11" t="str">
-        <x:v>赛事</x:v>
+        <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>岗位能力</x:v>
+        <x:v>课程</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str">
-        <x:v>competition_id, ability_id</x:v>
+        <x:v>course_ids -&gt; course_id</x:v>
       </x:c>
       <x:c r="F22" s="11" t="str">
-        <x:v>赛项能力要求转化为课程和实训依据。</x:v>
+        <x:v>岗位资源匹配可转译为课程和实训建议。</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="11" t="str">
+        <x:v>rel_company_industry</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="str">
+        <x:v>企业</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="str">
+        <x:v>行业</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="str">
+        <x:v>N:1</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="str">
+        <x:v>industry_code</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="str">
+        <x:v>企业按国民经济行业分类归类。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="11" t="str">
+        <x:v>rel_posting_job</x:v>
+      </x:c>
+      <x:c r="B24" s="11" t="str">
+        <x:v>招聘信息</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="str">
+        <x:v>岗位</x:v>
+      </x:c>
+      <x:c r="D24" s="11" t="str">
+        <x:v>N:1</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="str">
+        <x:v>posting_id -&gt; job_id</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="str">
+        <x:v>原始招聘标题归一到岗位库。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="11" t="str">
+        <x:v>rel_posting_company</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="str">
+        <x:v>招聘信息</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="str">
+        <x:v>企业</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="str">
+        <x:v>N:1</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="str">
+        <x:v>posting_id -&gt; company_id</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
+        <x:v>招聘企业归一到企业库。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="11" t="str">
+        <x:v>rel_trend_job</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="str">
+        <x:v>招聘趋势</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="str">
+        <x:v>岗位/产业链/城市</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="str">
+        <x:v>聚合</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="str">
+        <x:v>period, chain_id, job_id, city</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="str">
+        <x:v>按周期沉淀趋势统计，避免实时口径漂移。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="11" t="str">
+        <x:v>rel_tech_chain</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="str">
+        <x:v>新技术岗位匹配</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str">
+        <x:v>产业链</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="str">
+        <x:v>N:1</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str">
+        <x:v>chain_id -&gt; chain_id</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>新技术方向归属产业链，用于按链条过滤研判记录。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="24" hidden="0" customHeight="1">
+      <x:c r="A28" s="11" t="str">
+        <x:v>rel_tech_node</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="str">
+        <x:v>新技术岗位匹配</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="str">
+        <x:v>产业环节</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="str">
+        <x:v>N:1</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="str">
+        <x:v>industry_node_id -&gt; industry_node_id</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="str">
+        <x:v>新技术方向关联具体产业环节，支撑产业影响分析。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="11" t="str">
+        <x:v>rel_tech_job</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="str">
+        <x:v>新技术岗位匹配</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="str">
+        <x:v>岗位</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="str">
+        <x:v>N:1</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str">
+        <x:v>job_id -&gt; job_id</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="str">
+        <x:v>新技术方向关联新增或强化岗位，并可引用岗位职业路径。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="11" t="str">
+        <x:v>rel_tech_major</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="str">
+        <x:v>新技术岗位匹配</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="str">
+        <x:v>专业</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="str">
+        <x:v>N:M</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="str">
+        <x:v>major_codes -&gt; major_code</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="str">
+        <x:v>新技术方向推荐或关联多个专业，用于专业协同建设。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="11" t="str">
+        <x:v>rel_tech_course</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="str">
+        <x:v>新技术岗位匹配</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>课程</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="str">
+        <x:v>N:M</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="str">
+        <x:v>course_ids -&gt; course_id</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>新技术方向转译为课程或实训建议。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="11" t="str">
+        <x:v>rel_tech_ability</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="str">
+        <x:v>新技术岗位匹配</x:v>
+      </x:c>
+      <x:c r="C32" s="11" t="str">
+        <x:v>岗位能力</x:v>
+      </x:c>
+      <x:c r="D32" s="11" t="str">
+        <x:v>N:M</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="str">
+        <x:v>ability_ids -&gt; ability_id</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="str">
+        <x:v>新技术方向映射到岗位能力项和课程能力目标。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="11" t="str">
+        <x:v>rel_tech_trend</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>新技术岗位匹配</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>招聘趋势</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="str">
+        <x:v>N:1参考</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="str">
+        <x:v>job_id -&gt; job_id</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>紧缺度、薪资区间和人才缺口判断可回溯招聘趋势。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="11" t="str">
+        <x:v>rel_competition_major</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="str">
+        <x:v>赛事</x:v>
+      </x:c>
+      <x:c r="C34" s="11" t="str">
+        <x:v>专业</x:v>
+      </x:c>
+      <x:c r="D34" s="11" t="str">
+        <x:v>N:M</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="str">
+        <x:v>competition_id, major_code</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="str">
+        <x:v>赛项适配专业。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="11" t="str">
+        <x:v>rel_competition_ability</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="str">
+        <x:v>赛事</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="str">
+        <x:v>岗位能力</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="str">
+        <x:v>N:M</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="str">
+        <x:v>competition_id, ability_id</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str">
+        <x:v>赛项能力要求转化为课程和实训依据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="11" t="str">
         <x:v>rel_policy_context</x:v>
       </x:c>
-      <x:c r="B23" s="11" t="str">
+      <x:c r="B36" s="11" t="str">
         <x:v>政策</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="str">
+      <x:c r="C36" s="11" t="str">
         <x:v>产业链/专业/岗位</x:v>
       </x:c>
-      <x:c r="D23" s="11" t="str">
+      <x:c r="D36" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="str">
+      <x:c r="E36" s="11" t="str">
         <x:v>policy_id + object_id</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="str">
+      <x:c r="F36" s="11" t="str">
         <x:v>政策可关联多个产业、专业和岗位。</x:v>
       </x:c>
     </x:row>
@@ -8593,10 +9743,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>task_id</x:v>
+        <x:v>resource_match_id</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>任务ID</x:v>
+        <x:v>资源匹配ID</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>string</x:v>
@@ -8608,16 +9758,16 @@
         <x:v>PK</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>岗位典型工作任务主键。</x:v>
+        <x:v>岗位画像中专业、证书、企业等资源匹配结果的唯一标识。</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>task_bim_001</x:v>
+        <x:v>resmatch_bim_001</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>系统生成/模板导入</x:v>
+        <x:v>系统生成/AI生成后审核</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
-        <x:v>创建时</x:v>
+        <x:v>每次匹配</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str"/>
     </x:row>
@@ -8638,7 +9788,7 @@
         <x:v>FK</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>所属岗位。</x:v>
+        <x:v>被推荐资源服务的岗位。</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
         <x:v>job_bim_deepening</x:v>
@@ -8655,40 +9805,40 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>task_name</x:v>
+        <x:v>major_codes</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>任务名称</x:v>
+        <x:v>对接专业</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str">
-        <x:v>典型工作任务名称。</x:v>
+        <x:v>岗位画像推荐或关联的专业代码列表。</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>BIM模型深化与碰撞检查</x:v>
+        <x:v>440301,440304,440501</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>岗位画像/模板导入</x:v>
+        <x:v>专业库/规则匹配/人工复核</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>按项目维护</x:v>
-      </x:c>
-      <x:c r="J4" s="11" t="str"/>
+        <x:v>按版本</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str">
+        <x:v>关联01_专业库.major_code</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>task_description</x:v>
+        <x:v>certificate_ids</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>任务描述</x:v>
+        <x:v>推荐证书</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>text</x:v>
@@ -8698,53 +9848,57 @@
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str">
-        <x:v>任务工作内容、输入输出、交付标准。</x:v>
+        <x:v>岗位画像推荐的职业资格、职业技能等级或1+X证书ID列表。</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>基于施工图完成模型深化并输出碰撞报告</x:v>
+        <x:v>cert_bim_model,cert_bim_platform</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>招聘文本/专家维护</x:v>
+        <x:v>证书库/岗位能力匹配</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
         <x:v>按版本</x:v>
       </x:c>
-      <x:c r="J5" s="11" t="str"/>
+      <x:c r="J5" s="11" t="str">
+        <x:v>关联13_证书库</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>task_stage</x:v>
+        <x:v>company_ids</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>任务阶段</x:v>
+        <x:v>相关企业</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str">
-        <x:v>准备、实施、检查、交付、运维等。</x:v>
+        <x:v>岗位画像展示的代表企业或合作企业ID列表。</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>实施</x:v>
+        <x:v>company_glodon,company_pinming</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>人工维护</x:v>
+        <x:v>企业库/招聘信息库/人工复核</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>按项目维护</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="str"/>
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
+        <x:v>关联09_企业库</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="24" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
         <x:v>ability_ids</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>关联能力项</x:v>
+        <x:v>匹配能力项</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
         <x:v>text</x:v>
@@ -8754,27 +9908,27 @@
       </x:c>
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str">
-        <x:v>完成任务所需能力项ID列表。</x:v>
+        <x:v>支撑专业、证书和企业匹配的岗位能力项ID。</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>ability_bim_model,ability_issue_report</x:v>
+        <x:v>ability_bim_model,ability_coordination</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
         <x:v>岗位能力库</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>按项目维护</x:v>
+        <x:v>按版本</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str">
-        <x:v>多值可拆关系表</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
+        <x:v>关联08_岗位能力库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>evidence_source</x:v>
+        <x:v>course_ids</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>证据来源</x:v>
+        <x:v>建议课程/实训</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
         <x:v>text</x:v>
@@ -8784,18 +9938,164 @@
       </x:c>
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str">
-        <x:v>任务来自招聘文本、职业标准、企业访谈或专家维护。</x:v>
+        <x:v>由岗位资源匹配反推的课程或实训项目ID。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>招聘文本+职业标准</x:v>
+        <x:v>course_bim_app,course_project_delivery</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>多来源</x:v>
+        <x:v>课程库/AI生成后审核</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>按批次</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="str"/>
+        <x:v>按学年</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str">
+        <x:v>关联14_课程库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" hidden="0" customHeight="1">
+      <x:c r="A9" s="12" t="str">
+        <x:v>match_basis</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>匹配依据</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str"/>
+      <x:c r="F9" s="11" t="str">
+        <x:v>说明证书、专业、企业与岗位能力或任务之间的对应关系。</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="str">
+        <x:v>BIM模型创建、施工图深化与工程数据协同能力共同支撑</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="str">
+        <x:v>招聘文本/职业标准/课程资料/AI生成后审核</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
+        <x:v>每次匹配</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str"/>
+    </x:row>
+    <x:row r="10" ht="24" hidden="0" customHeight="1">
+      <x:c r="A10" s="12" t="str">
+        <x:v>evidence_source_ids</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>证据来源</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str"/>
+      <x:c r="F10" s="11" t="str">
+        <x:v>支撑匹配的招聘批次、证书目录、专业目录、企业资料或人工复核记录。</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>batch_job_202606,cert_catalog_2026,major_catalog_2021</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="str">
+        <x:v>数据来源库/采集批次</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="str">
+        <x:v>每次匹配</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="str"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="12" t="str">
+        <x:v>ai_generated_flag</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>是否AI生成</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>该匹配记录是否由AI生成或辅助生成。</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str">
+        <x:v>系统生成</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="str">
+        <x:v>每次匹配</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="str"/>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="12" t="str">
+        <x:v>review_status</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>审核状态</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>待审核、已审核、需补充证据、停用。</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str">
+        <x:v>待审核</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="str">
+        <x:v>运营/专家复核</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="str">
+        <x:v>按版本</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="str"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="12" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>datetime</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str"/>
+      <x:c r="F13" s="11" t="str">
+        <x:v>记录最近生成或复核时间。</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str">
+        <x:v>2026-06-23 13:30</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str">
+        <x:v>系统生成</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str">
+        <x:v>每次更新</x:v>
+      </x:c>
+      <x:c r="J13" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/V1.0需求（2026.6.11）/官方数据/DW_专业建设数据模型设计_岗位所属行业更新.xlsx
+++ b/V1.0需求（2026.6.11）/官方数据/DW_专业建设数据模型设计_岗位所属行业更新.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_总览" sheetId="1" r:id="R87df9525d9e349cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_专业库" sheetId="2" r:id="R3af34b0bf9564d6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_行业库" sheetId="3" r:id="R99323a3891e24af2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_产业链库" sheetId="4" r:id="R5e0c96d8d982400f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_产业环节库" sheetId="5" r:id="Rb40c7d4c75314209"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04A_产业环节关系库" sheetId="6" r:id="R0ea90bfe2e714969"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_职业库" sheetId="7" r:id="R189167a99d064858"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_岗位库" sheetId="8" r:id="Rf655683dadf4485d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06A_岗位资源匹配库" sheetId="9" r:id="R8a53c251a7284d01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_岗位任务库" sheetId="10" r:id="R759d9ad0b02f48d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_岗位能力库" sheetId="11" r:id="R08461603aa684a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_企业库" sheetId="12" r:id="R266c169e8a174faf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_招聘信息库" sheetId="13" r:id="R684342c0dea740fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_招聘趋势库" sheetId="14" r:id="Ra452bf7a47c14866"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11A_新技术岗位匹配库" sheetId="15" r:id="R74c0aea720304ab9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_赛事库" sheetId="16" r:id="R4b933eca33a64e42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_证书库" sheetId="17" r:id="R5182bdcc9c254fec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_课程库" sheetId="18" r:id="R74e94268d3f44d0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_政策库" sheetId="19" r:id="R009737da634f46cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_初始化批次库" sheetId="20" r:id="R0162b8ed7ec14633"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_数据来源目录" sheetId="21" r:id="R287e6876a16f4320"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_关联关系" sheetId="22" r:id="R1fb86b84758e4ec4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_总览" sheetId="1" r:id="R5abb546ba9fc4819"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_专业库" sheetId="2" r:id="R94a1f6cb5dc5460f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_行业库" sheetId="3" r:id="Rdf68abdb6f19499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_产业链库" sheetId="4" r:id="R92cb92efa93d454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_产业环节库" sheetId="5" r:id="Rf1daf925ac3b4363"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04A_产业环节关系库" sheetId="6" r:id="R3ee7882868d44aad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_职业库" sheetId="7" r:id="R759da5c4d8554534"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_岗位库" sheetId="8" r:id="Rb0e7ec3f3b7349ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06A_岗位资源匹配库" sheetId="9" r:id="R48875828199b46d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_岗位任务库" sheetId="10" r:id="R872ed653ce01413b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_岗位能力库" sheetId="11" r:id="R037d1aa6446d42ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_企业库" sheetId="12" r:id="Ra5567f36293245ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_招聘信息库" sheetId="13" r:id="Re264dc07a33e4e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_招聘趋势库" sheetId="14" r:id="R14b1358879a64c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11A_新技术岗位匹配库" sheetId="15" r:id="R1532367684cf4776"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_赛事库" sheetId="16" r:id="Rcb0faca6bb824d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_证书库" sheetId="17" r:id="R371652958b6a4239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_课程库" sheetId="18" r:id="Rc8fdb166ed704982"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_政策库" sheetId="19" r:id="Rf4486ce65ab946d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_初始化批次库" sheetId="20" r:id="R4f8f2b3058124683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_数据来源目录" sheetId="21" r:id="R0e2865f7ec484b68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_关联关系" sheetId="22" r:id="Rb96367881c3c464b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6652,90 +6652,90 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="11" t="str">
-        <x:v>rel_job_task</x:v>
+        <x:v>rel_job_major</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
         <x:v>岗位</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>岗位任务</x:v>
+        <x:v>专业</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>1:N</x:v>
+        <x:v>N:M</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>job_id -&gt; task_id</x:v>
+        <x:v>related_major_codes -&gt; major_code</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>岗位详情中的典型工作任务。</x:v>
+        <x:v>岗位画像可直接关联多个专业，用于从岗位侧回溯专业建设对象。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="11" t="str">
-        <x:v>rel_job_ability</x:v>
+        <x:v>rel_job_task</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
         <x:v>岗位</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>岗位能力</x:v>
+        <x:v>岗位任务</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
         <x:v>1:N</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>job_id -&gt; ability_id</x:v>
+        <x:v>job_id -&gt; task_id</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>岗位知识、技能、素养能力项。</x:v>
+        <x:v>岗位详情中的典型工作任务。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="11" t="str">
-        <x:v>rel_task_ability</x:v>
+        <x:v>rel_job_ability</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>岗位任务</x:v>
+        <x:v>岗位</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
         <x:v>岗位能力</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>N:M</x:v>
+        <x:v>1:N</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>task_id, ability_id</x:v>
+        <x:v>job_id -&gt; ability_id</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
-        <x:v>任务需要若干能力支撑，适合拆为关系表。</x:v>
+        <x:v>岗位知识、技能、素养能力项。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="11" t="str">
-        <x:v>rel_job_course</x:v>
+        <x:v>rel_task_ability</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>岗位</x:v>
+        <x:v>岗位任务</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>课程</x:v>
+        <x:v>岗位能力</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
-        <x:v>job_id, course_id</x:v>
+        <x:v>task_id, ability_id</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
-        <x:v>课程支撑岗位能力和岗位建设。</x:v>
+        <x:v>任务需要若干能力支撑，适合拆为关系表。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="11" t="str">
-        <x:v>rel_ability_course</x:v>
+        <x:v>rel_job_course</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>岗位能力</x:v>
+        <x:v>岗位</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
         <x:v>课程</x:v>
@@ -6744,449 +6744,469 @@
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>ability_id, course_id</x:v>
+        <x:v>job_id, course_id</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
-        <x:v>课程目标映射能力项。</x:v>
+        <x:v>课程支撑岗位能力和岗位建设。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="11" t="str">
-        <x:v>rel_job_certificate</x:v>
+        <x:v>rel_ability_course</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>岗位</x:v>
+        <x:v>岗位能力</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>证书</x:v>
+        <x:v>课程</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>job_id, certificate_id</x:v>
+        <x:v>ability_id, course_id</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
-        <x:v>岗位可推荐多个证书，一个证书适配多个岗位。</x:v>
+        <x:v>课程目标映射能力项。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="11" t="str">
-        <x:v>rel_job_company</x:v>
+        <x:v>rel_job_certificate</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
         <x:v>岗位</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>企业</x:v>
+        <x:v>证书</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>job_id, company_id</x:v>
+        <x:v>job_id, certificate_id</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
-        <x:v>企业样本和主要招聘岗位关系。</x:v>
+        <x:v>岗位可推荐多个证书，一个证书适配多个岗位。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="11" t="str">
-        <x:v>rel_resource_job</x:v>
+        <x:v>rel_job_company</x:v>
       </x:c>
       <x:c r="B17" s="11" t="str">
-        <x:v>岗位资源匹配</x:v>
+        <x:v>岗位</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>岗位</x:v>
+        <x:v>企业</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>N:1</x:v>
+        <x:v>N:M</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str">
-        <x:v>job_id -&gt; job_id</x:v>
+        <x:v>job_id, company_id</x:v>
       </x:c>
       <x:c r="F17" s="11" t="str">
-        <x:v>岗位画像资源匹配归属具体岗位。</x:v>
+        <x:v>企业样本和主要招聘岗位关系。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="11" t="str">
-        <x:v>rel_resource_major</x:v>
+        <x:v>rel_resource_job</x:v>
       </x:c>
       <x:c r="B18" s="11" t="str">
         <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>专业</x:v>
+        <x:v>岗位</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>N:M</x:v>
+        <x:v>N:1</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>major_codes -&gt; major_code</x:v>
+        <x:v>job_id -&gt; job_id</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
-        <x:v>岗位画像中的对接专业可回溯到专业库。</x:v>
+        <x:v>岗位画像资源匹配归属具体岗位。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="11" t="str">
-        <x:v>rel_resource_certificate</x:v>
+        <x:v>rel_resource_major</x:v>
       </x:c>
       <x:c r="B19" s="11" t="str">
         <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>证书</x:v>
+        <x:v>专业</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str">
-        <x:v>certificate_ids -&gt; certificate_id</x:v>
+        <x:v>major_codes -&gt; major_code</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>岗位画像中的推荐证书可回溯到证书库。</x:v>
+        <x:v>岗位画像中的对接专业可回溯到专业库。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="11" t="str">
-        <x:v>rel_resource_company</x:v>
+        <x:v>rel_resource_certificate</x:v>
       </x:c>
       <x:c r="B20" s="11" t="str">
         <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>企业</x:v>
+        <x:v>证书</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>company_ids -&gt; company_id</x:v>
+        <x:v>certificate_ids -&gt; certificate_id</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>岗位画像中的相关企业可回溯到企业库。</x:v>
+        <x:v>岗位画像中的推荐证书可回溯到证书库。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="11" t="str">
-        <x:v>rel_resource_ability</x:v>
+        <x:v>rel_resource_company</x:v>
       </x:c>
       <x:c r="B21" s="11" t="str">
         <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>岗位能力</x:v>
+        <x:v>企业</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>ability_ids -&gt; ability_id</x:v>
+        <x:v>company_ids -&gt; company_id</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
-        <x:v>专业、证书、企业推荐依据可追溯到岗位能力项。</x:v>
+        <x:v>岗位画像中的相关企业可回溯到企业库。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="11" t="str">
-        <x:v>rel_resource_course</x:v>
+        <x:v>rel_resource_ability</x:v>
       </x:c>
       <x:c r="B22" s="11" t="str">
         <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>课程</x:v>
+        <x:v>岗位能力</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str">
-        <x:v>course_ids -&gt; course_id</x:v>
+        <x:v>ability_ids -&gt; ability_id</x:v>
       </x:c>
       <x:c r="F22" s="11" t="str">
-        <x:v>岗位资源匹配可转译为课程和实训建议。</x:v>
+        <x:v>专业、证书、企业推荐依据可追溯到岗位能力项。</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="11" t="str">
-        <x:v>rel_company_industry</x:v>
+        <x:v>rel_resource_course</x:v>
       </x:c>
       <x:c r="B23" s="11" t="str">
-        <x:v>企业</x:v>
+        <x:v>岗位资源匹配</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>行业</x:v>
+        <x:v>课程</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>N:1</x:v>
+        <x:v>N:M</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str">
-        <x:v>industry_code</x:v>
+        <x:v>course_ids -&gt; course_id</x:v>
       </x:c>
       <x:c r="F23" s="11" t="str">
-        <x:v>企业按国民经济行业分类归类。</x:v>
+        <x:v>岗位资源匹配可转译为课程和实训建议。</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="11" t="str">
-        <x:v>rel_posting_job</x:v>
+        <x:v>rel_company_industry</x:v>
       </x:c>
       <x:c r="B24" s="11" t="str">
-        <x:v>招聘信息</x:v>
+        <x:v>企业</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>岗位</x:v>
+        <x:v>行业</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
         <x:v>N:1</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
-        <x:v>posting_id -&gt; job_id</x:v>
+        <x:v>industry_code</x:v>
       </x:c>
       <x:c r="F24" s="11" t="str">
-        <x:v>原始招聘标题归一到岗位库。</x:v>
+        <x:v>企业按国民经济行业分类归类。</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="11" t="str">
-        <x:v>rel_posting_company</x:v>
+        <x:v>rel_posting_job</x:v>
       </x:c>
       <x:c r="B25" s="11" t="str">
         <x:v>招聘信息</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>企业</x:v>
+        <x:v>岗位</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
         <x:v>N:1</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
-        <x:v>posting_id -&gt; company_id</x:v>
+        <x:v>posting_id -&gt; job_id</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>招聘企业归一到企业库。</x:v>
+        <x:v>原始招聘标题归一到岗位库。</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="11" t="str">
-        <x:v>rel_trend_job</x:v>
+        <x:v>rel_posting_company</x:v>
       </x:c>
       <x:c r="B26" s="11" t="str">
-        <x:v>招聘趋势</x:v>
+        <x:v>招聘信息</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>岗位/产业链/城市</x:v>
+        <x:v>企业</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>聚合</x:v>
+        <x:v>N:1</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
-        <x:v>period, chain_id, job_id, city</x:v>
+        <x:v>posting_id -&gt; company_id</x:v>
       </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>按周期沉淀趋势统计，避免实时口径漂移。</x:v>
+        <x:v>招聘企业归一到企业库。</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="11" t="str">
+        <x:v>rel_trend_job</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="str">
+        <x:v>招聘趋势</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str">
+        <x:v>岗位/产业链/城市</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="str">
+        <x:v>聚合</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str">
+        <x:v>period, chain_id, job_id, city</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>按周期沉淀趋势统计，避免实时口径漂移。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="11" t="str">
         <x:v>rel_tech_chain</x:v>
-      </x:c>
-      <x:c r="B27" s="11" t="str">
-        <x:v>新技术岗位匹配</x:v>
-      </x:c>
-      <x:c r="C27" s="11" t="str">
-        <x:v>产业链</x:v>
-      </x:c>
-      <x:c r="D27" s="11" t="str">
-        <x:v>N:1</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="str">
-        <x:v>chain_id -&gt; chain_id</x:v>
-      </x:c>
-      <x:c r="F27" s="11" t="str">
-        <x:v>新技术方向归属产业链，用于按链条过滤研判记录。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="24" hidden="0" customHeight="1">
-      <x:c r="A28" s="11" t="str">
-        <x:v>rel_tech_node</x:v>
       </x:c>
       <x:c r="B28" s="11" t="str">
         <x:v>新技术岗位匹配</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>产业环节</x:v>
+        <x:v>产业链</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
         <x:v>N:1</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
-        <x:v>industry_node_id -&gt; industry_node_id</x:v>
+        <x:v>chain_id -&gt; chain_id</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>新技术方向关联具体产业环节，支撑产业影响分析。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="15" hidden="0" customHeight="1">
+        <x:v>新技术方向归属产业链，用于按链条过滤研判记录。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="24" hidden="0" customHeight="1">
       <x:c r="A29" s="11" t="str">
-        <x:v>rel_tech_job</x:v>
+        <x:v>rel_tech_node</x:v>
       </x:c>
       <x:c r="B29" s="11" t="str">
         <x:v>新技术岗位匹配</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>岗位</x:v>
+        <x:v>产业环节</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
         <x:v>N:1</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
-        <x:v>job_id -&gt; job_id</x:v>
+        <x:v>industry_node_id -&gt; industry_node_id</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>新技术方向关联新增或强化岗位，并可引用岗位职业路径。</x:v>
+        <x:v>新技术方向关联具体产业环节，支撑产业影响分析。</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="11" t="str">
-        <x:v>rel_tech_major</x:v>
+        <x:v>rel_tech_job</x:v>
       </x:c>
       <x:c r="B30" s="11" t="str">
         <x:v>新技术岗位匹配</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>专业</x:v>
+        <x:v>岗位</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>N:M</x:v>
+        <x:v>N:1</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str">
-        <x:v>major_codes -&gt; major_code</x:v>
+        <x:v>job_id -&gt; job_id</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>新技术方向推荐或关联多个专业，用于专业协同建设。</x:v>
+        <x:v>新技术方向关联新增或强化岗位，并可引用岗位职业路径。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="11" t="str">
-        <x:v>rel_tech_course</x:v>
+        <x:v>rel_tech_major</x:v>
       </x:c>
       <x:c r="B31" s="11" t="str">
         <x:v>新技术岗位匹配</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>课程</x:v>
+        <x:v>专业</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>course_ids -&gt; course_id</x:v>
+        <x:v>major_codes -&gt; major_code</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>新技术方向转译为课程或实训建议。</x:v>
+        <x:v>新技术方向推荐或关联多个专业，用于专业协同建设。</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="11" t="str">
-        <x:v>rel_tech_ability</x:v>
+        <x:v>rel_tech_course</x:v>
       </x:c>
       <x:c r="B32" s="11" t="str">
         <x:v>新技术岗位匹配</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
-        <x:v>岗位能力</x:v>
+        <x:v>课程</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
-        <x:v>ability_ids -&gt; ability_id</x:v>
+        <x:v>course_ids -&gt; course_id</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>新技术方向映射到岗位能力项和课程能力目标。</x:v>
+        <x:v>新技术方向转译为课程或实训建议。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="11" t="str">
-        <x:v>rel_tech_trend</x:v>
+        <x:v>rel_tech_ability</x:v>
       </x:c>
       <x:c r="B33" s="11" t="str">
         <x:v>新技术岗位匹配</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>招聘趋势</x:v>
+        <x:v>岗位能力</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>N:1参考</x:v>
+        <x:v>N:M</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>job_id -&gt; job_id</x:v>
+        <x:v>ability_ids -&gt; ability_id</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>紧缺度、薪资区间和人才缺口判断可回溯招聘趋势。</x:v>
+        <x:v>新技术方向映射到岗位能力项和课程能力目标。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="11" t="str">
-        <x:v>rel_competition_major</x:v>
+        <x:v>rel_tech_trend</x:v>
       </x:c>
       <x:c r="B34" s="11" t="str">
-        <x:v>赛事</x:v>
+        <x:v>新技术岗位匹配</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>专业</x:v>
+        <x:v>招聘趋势</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>N:M</x:v>
+        <x:v>N:1参考</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>competition_id, major_code</x:v>
+        <x:v>job_id -&gt; job_id</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
-        <x:v>赛项适配专业。</x:v>
+        <x:v>紧缺度、薪资区间和人才缺口判断可回溯招聘趋势。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="11" t="str">
-        <x:v>rel_competition_ability</x:v>
+        <x:v>rel_competition_major</x:v>
       </x:c>
       <x:c r="B35" s="11" t="str">
         <x:v>赛事</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>岗位能力</x:v>
+        <x:v>专业</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>competition_id, ability_id</x:v>
+        <x:v>competition_id, major_code</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
-        <x:v>赛项能力要求转化为课程和实训依据。</x:v>
+        <x:v>赛项适配专业。</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="11" t="str">
-        <x:v>rel_policy_context</x:v>
+        <x:v>rel_competition_ability</x:v>
       </x:c>
       <x:c r="B36" s="11" t="str">
-        <x:v>政策</x:v>
+        <x:v>赛事</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>产业链/专业/岗位</x:v>
+        <x:v>岗位能力</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
         <x:v>N:M</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
+        <x:v>competition_id, ability_id</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="str">
+        <x:v>赛项能力要求转化为课程和实训依据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="11" t="str">
+        <x:v>rel_policy_context</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="str">
+        <x:v>政策</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="str">
+        <x:v>产业链/专业/岗位</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="str">
+        <x:v>N:M</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="str">
         <x:v>policy_id + object_id</x:v>
       </x:c>
-      <x:c r="F36" s="11" t="str">
+      <x:c r="F37" s="11" t="str">
         <x:v>政策可关联多个产业、专业和岗位。</x:v>
       </x:c>
     </x:row>
@@ -9272,44 +9292,42 @@
       </x:c>
       <x:c r="J7" s="11" t="str"/>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
+    <x:row r="8" ht="24" hidden="0" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>industry_node_id</x:v>
+        <x:v>related_major_codes</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>所属产业环节ID</x:v>
+        <x:v>关联专业</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str">
-        <x:v>岗位承接的产业节点。</x:v>
+        <x:v>岗位可对接或支撑的专业代码列表，用于从岗位画像直接回连专业库。</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>node_bim_platform</x:v>
+        <x:v>440301,440304</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>产业环节库</x:v>
+        <x:v>专业库/岗位画像/规则匹配</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>按项目维护</x:v>
+        <x:v>按版本</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str">
-        <x:v>关联04_产业环节库</x:v>
+        <x:v>关联01_专业库.major_code</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="12" t="str">
-        <x:v>chain_id</x:v>
+        <x:v>industry_node_id</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>所属产业链ID</x:v>
+        <x:v>所属产业环节ID</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>string</x:v>
@@ -9321,27 +9339,27 @@
         <x:v>FK</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>岗位归属产业链。</x:v>
+        <x:v>岗位承接的产业节点。</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>chain_platform</x:v>
+        <x:v>node_bim_platform</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>产业链库</x:v>
+        <x:v>产业环节库</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
         <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str">
-        <x:v>关联03_产业链库</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="24" hidden="0" customHeight="1">
+        <x:v>关联04_产业环节库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="12" t="str">
-        <x:v>industry_code</x:v>
+        <x:v>chain_id</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>所属行业代码</x:v>
+        <x:v>所属产业链ID</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>string</x:v>
@@ -9353,62 +9371,62 @@
         <x:v>FK</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>岗位所属行业代码，按岗位归属行业映射到国民经济行业分类。</x:v>
+        <x:v>岗位归属产业链。</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>I65</x:v>
+        <x:v>chain_platform</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>行业库/招聘归并/人工维护</x:v>
+        <x:v>产业链库</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
-        <x:v>按批次</x:v>
+        <x:v>按项目维护</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str">
-        <x:v>关联02_行业库</x:v>
+        <x:v>关联03_产业链库</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" hidden="0" customHeight="1">
       <x:c r="A11" s="12" t="str">
-        <x:v>industry_name</x:v>
+        <x:v>industry_code</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>所属行业名称</x:v>
+        <x:v>所属行业代码</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>string</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>IDX</x:v>
+        <x:v>FK</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>岗位所属行业展示名称，冗余自行业库用于页面展示和筛选。</x:v>
+        <x:v>岗位所属行业代码，按岗位归属行业映射到国民经济行业分类。</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>软件和信息技术服务业</x:v>
+        <x:v>I65</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>行业库/规则映射</x:v>
+        <x:v>行业库/招聘归并/人工维护</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
         <x:v>按批次</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str">
-        <x:v>冗余展示字段</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
+        <x:v>关联02_行业库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="24" hidden="0" customHeight="1">
       <x:c r="A12" s="12" t="str">
-        <x:v>job_level</x:v>
+        <x:v>industry_name</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>岗位层级</x:v>
+        <x:v>所属行业名称</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
         <x:v>否</x:v>
@@ -9417,127 +9435,131 @@
         <x:v>IDX</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
-        <x:v>初级、中级、高级。</x:v>
+        <x:v>岗位所属行业展示名称，冗余自行业库用于页面展示和筛选。</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>中级</x:v>
+        <x:v>软件和信息技术服务业</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
-        <x:v>招聘归并/运营维护</x:v>
+        <x:v>行业库/规则映射</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
         <x:v>按批次</x:v>
       </x:c>
-      <x:c r="J12" s="11" t="str"/>
+      <x:c r="J12" s="11" t="str">
+        <x:v>冗余展示字段</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="12" t="str">
-        <x:v>salary_range</x:v>
+        <x:v>job_level</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>薪资范围</x:v>
+        <x:v>岗位层级</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="str"/>
+      <x:c r="E13" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
       <x:c r="F13" s="11" t="str">
-        <x:v>招聘样本统计后的薪资区间。</x:v>
+        <x:v>初级、中级、高级。</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>10K-18K</x:v>
+        <x:v>中级</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str">
-        <x:v>招聘信息库</x:v>
+        <x:v>招聘归并/运营维护</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str">
-        <x:v>月度/批次</x:v>
+        <x:v>按批次</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="12" t="str">
-        <x:v>demand_level</x:v>
+        <x:v>salary_range</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>需求等级</x:v>
+        <x:v>薪资范围</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+      <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str">
-        <x:v>高、中、低、待评估。</x:v>
+        <x:v>招聘样本统计后的薪资区间。</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>高</x:v>
+        <x:v>10K-18K</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str">
-        <x:v>招聘趋势库/规则</x:v>
+        <x:v>招聘信息库</x:v>
       </x:c>
       <x:c r="I14" s="11" t="str">
-        <x:v>月度</x:v>
+        <x:v>月度/批次</x:v>
       </x:c>
       <x:c r="J14" s="11" t="str"/>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="12" t="str">
-        <x:v>demand_volume</x:v>
+        <x:v>demand_level</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>需求量</x:v>
+        <x:v>需求等级</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="str"/>
+      <x:c r="E15" s="11" t="str">
+        <x:v>IDX</x:v>
+      </x:c>
       <x:c r="F15" s="11" t="str">
-        <x:v>统计周期内招聘样本量或需求指数。</x:v>
+        <x:v>高、中、低、待评估。</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>2176</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
-        <x:v>招聘信息库/招聘趋势库</x:v>
+        <x:v>招聘趋势库/规则</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str">
-        <x:v>月度/批次</x:v>
+        <x:v>月度</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str"/>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="12" t="str">
-        <x:v>education</x:v>
+        <x:v>demand_volume</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
-        <x:v>学历要求</x:v>
+        <x:v>需求量</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str">
-        <x:v>岗位常见学历门槛。</x:v>
+        <x:v>统计周期内招聘样本量或需求指数。</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>大专及以上</x:v>
+        <x:v>2176</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str">
-        <x:v>招聘信息库</x:v>
+        <x:v>招聘信息库/招聘趋势库</x:v>
       </x:c>
       <x:c r="I16" s="11" t="str">
         <x:v>月度/批次</x:v>
@@ -9546,10 +9568,10 @@
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="12" t="str">
-        <x:v>experience</x:v>
+        <x:v>education</x:v>
       </x:c>
       <x:c r="B17" s="11" t="str">
-        <x:v>经验要求</x:v>
+        <x:v>学历要求</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>enum</x:v>
@@ -9559,10 +9581,10 @@
       </x:c>
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str">
-        <x:v>岗位常见经验要求。</x:v>
+        <x:v>岗位常见学历门槛。</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str">
-        <x:v>1-3年</x:v>
+        <x:v>大专及以上</x:v>
       </x:c>
       <x:c r="H17" s="11" t="str">
         <x:v>招聘信息库</x:v>
@@ -9572,40 +9594,40 @@
       </x:c>
       <x:c r="J17" s="11" t="str"/>
     </x:row>
-    <x:row r="18" ht="24" hidden="0" customHeight="1">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="12" t="str">
-        <x:v>career_path</x:v>
+        <x:v>experience</x:v>
       </x:c>
       <x:c r="B18" s="11" t="str">
-        <x:v>职业发展路径</x:v>
+        <x:v>经验要求</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str">
-        <x:v>从初级到高级或管理方向的发展路径。</x:v>
+        <x:v>岗位常见经验要求。</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str">
-        <x:v>BIM建模员 -&gt; BIM深化设计工程师 -&gt; BIM项目经理</x:v>
+        <x:v>1-3年</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str">
-        <x:v>岗位画像/人工维护</x:v>
+        <x:v>招聘信息库</x:v>
       </x:c>
       <x:c r="I18" s="11" t="str">
-        <x:v>按版本</x:v>
+        <x:v>月度/批次</x:v>
       </x:c>
       <x:c r="J18" s="11" t="str"/>
     </x:row>
     <x:row r="19" ht="24" hidden="0" customHeight="1">
       <x:c r="A19" s="12" t="str">
-        <x:v>work_summary</x:v>
+        <x:v>career_path</x:v>
       </x:c>
       <x:c r="B19" s="11" t="str">
-        <x:v>工作内容概述</x:v>
+        <x:v>职业发展路径</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
         <x:v>text</x:v>
@@ -9615,25 +9637,25 @@
       </x:c>
       <x:c r="E19" s="11" t="str"/>
       <x:c r="F19" s="11" t="str">
-        <x:v>岗位职责摘要。</x:v>
+        <x:v>从初级到高级或管理方向的发展路径。</x:v>
       </x:c>
       <x:c r="G19" s="11" t="str">
-        <x:v>负责模型深化、碰撞检查、工程量提取与协同交付</x:v>
+        <x:v>BIM建模员 -&gt; BIM深化设计工程师 -&gt; BIM项目经理</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str">
-        <x:v>招聘文本/AI生成后审核</x:v>
+        <x:v>岗位画像/人工维护</x:v>
       </x:c>
       <x:c r="I19" s="11" t="str">
         <x:v>按版本</x:v>
       </x:c>
       <x:c r="J19" s="11" t="str"/>
     </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
+    <x:row r="20" ht="24" hidden="0" customHeight="1">
       <x:c r="A20" s="12" t="str">
-        <x:v>keywords</x:v>
+        <x:v>work_summary</x:v>
       </x:c>
       <x:c r="B20" s="11" t="str">
-        <x:v>关键词</x:v>
+        <x:v>工作内容概述</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
         <x:v>text</x:v>
@@ -9641,52 +9663,80 @@
       <x:c r="D20" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="str">
-        <x:v>IDX</x:v>
-      </x:c>
+      <x:c r="E20" s="11" t="str"/>
       <x:c r="F20" s="11" t="str">
-        <x:v>岗位能力、工具、场景关键词。</x:v>
+        <x:v>岗位职责摘要。</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str">
-        <x:v>BIM、Revit、碰撞检查</x:v>
+        <x:v>负责模型深化、碰撞检查、工程量提取与协同交付</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str">
-        <x:v>招聘文本/岗位画像</x:v>
+        <x:v>招聘文本/AI生成后审核</x:v>
       </x:c>
       <x:c r="I20" s="11" t="str">
-        <x:v>按批次</x:v>
+        <x:v>按版本</x:v>
       </x:c>
       <x:c r="J20" s="11" t="str"/>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="12" t="str">
-        <x:v>source_batch_id</x:v>
+        <x:v>keywords</x:v>
       </x:c>
       <x:c r="B21" s="11" t="str">
-        <x:v>来源批次ID</x:v>
+        <x:v>关键词</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>FK</x:v>
+        <x:v>IDX</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
-        <x:v>岗位来自哪次采集或初始化批次。</x:v>
+        <x:v>岗位能力、工具、场景关键词。</x:v>
       </x:c>
       <x:c r="G21" s="11" t="str">
-        <x:v>batch_202606</x:v>
+        <x:v>BIM、Revit、碰撞检查</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str">
-        <x:v>采集批次库</x:v>
+        <x:v>招聘文本/岗位画像</x:v>
       </x:c>
       <x:c r="I21" s="11" t="str">
         <x:v>按批次</x:v>
       </x:c>
       <x:c r="J21" s="11" t="str"/>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="12" t="str">
+        <x:v>source_batch_id</x:v>
+      </x:c>
+      <x:c r="B22" s="11" t="str">
+        <x:v>来源批次ID</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="str">
+        <x:v>岗位来自哪次采集或初始化批次。</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="str">
+        <x:v>batch_202606</x:v>
+      </x:c>
+      <x:c r="H22" s="11" t="str">
+        <x:v>采集批次库</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="str">
+        <x:v>按批次</x:v>
+      </x:c>
+      <x:c r="J22" s="11" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
